--- a/research/traditional_assets/database/data/brazil/brazil_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_telecom_wireless.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09461647217374625</v>
+        <v>0.0943244761683555</v>
       </c>
       <c r="C2">
-        <v>7876.422636551131</v>
+        <v>7835.89905341407</v>
       </c>
       <c r="D2">
-        <v>7456.322636551131</v>
+        <v>7501.19105341407</v>
       </c>
       <c r="E2">
-        <v>-2872.7</v>
+        <v>-2787.308</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>85.39200000000001</v>
       </c>
       <c r="G2">
         <v>420.1</v>
@@ -1457,28 +1457,28 @@
         <v>1520.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.2952176</v>
       </c>
       <c r="N2">
-        <v>1520.9</v>
+        <v>1516.6047824</v>
       </c>
       <c r="O2">
-        <v>517.1059999999999</v>
+        <v>515.6456260159999</v>
       </c>
       <c r="P2">
-        <v>1003.794</v>
+        <v>1000.959156384</v>
       </c>
       <c r="Q2">
-        <v>1924.894</v>
+        <v>1922.059156384</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09461647217374625</v>
+        <v>0.09494191532157122</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6404838951546503</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>354.0914900330078</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0943244761683555</v>
+        <v>0.09403248016296477</v>
       </c>
       <c r="C3">
-        <v>7835.89905341407</v>
+        <v>7795.918730687747</v>
       </c>
       <c r="D3">
-        <v>7501.19105341407</v>
+        <v>7546.602730687747</v>
       </c>
       <c r="E3">
-        <v>-2787.308</v>
+        <v>-2701.916</v>
       </c>
       <c r="F3">
-        <v>85.39200000000001</v>
+        <v>170.784</v>
       </c>
       <c r="G3">
         <v>420.1</v>
@@ -1539,28 +1539,28 @@
         <v>1520.9</v>
       </c>
       <c r="M3">
-        <v>4.2952176</v>
+        <v>8.5904352</v>
       </c>
       <c r="N3">
-        <v>1516.6047824</v>
+        <v>1512.3095648</v>
       </c>
       <c r="O3">
-        <v>515.6456260159999</v>
+        <v>514.1852520319999</v>
       </c>
       <c r="P3">
-        <v>1000.959156384</v>
+        <v>998.1243127679998</v>
       </c>
       <c r="Q3">
-        <v>1922.059156384</v>
+        <v>1919.224312768</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09494191532157122</v>
+        <v>0.09527400016629058</v>
       </c>
       <c r="T3">
-        <v>0.6404838951546503</v>
+        <v>0.6448120739298541</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>354.0914900330078</v>
+        <v>177.0457450165039</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09403248016296477</v>
+        <v>0.09374048415757404</v>
       </c>
       <c r="C4">
-        <v>7795.918730687747</v>
+        <v>7756.491595047246</v>
       </c>
       <c r="D4">
-        <v>7546.602730687747</v>
+        <v>7592.567595047246</v>
       </c>
       <c r="E4">
-        <v>-2701.916</v>
+        <v>-2616.524</v>
       </c>
       <c r="F4">
-        <v>170.784</v>
+        <v>256.176</v>
       </c>
       <c r="G4">
         <v>420.1</v>
@@ -1621,28 +1621,28 @@
         <v>1520.9</v>
       </c>
       <c r="M4">
-        <v>8.5904352</v>
+        <v>12.8856528</v>
       </c>
       <c r="N4">
-        <v>1512.3095648</v>
+        <v>1508.0143472</v>
       </c>
       <c r="O4">
-        <v>514.1852520319999</v>
+        <v>512.7248780479999</v>
       </c>
       <c r="P4">
-        <v>998.1243127679998</v>
+        <v>995.2894691519998</v>
       </c>
       <c r="Q4">
-        <v>1919.224312768</v>
+        <v>1916.389469152</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09527400016629058</v>
+        <v>0.09561293212121035</v>
       </c>
       <c r="T4">
-        <v>0.6448120739298541</v>
+        <v>0.6492294935045466</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>177.0457450165039</v>
+        <v>118.0304966776693</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09374048415757404</v>
+        <v>0.09344848815218329</v>
       </c>
       <c r="C5">
-        <v>7756.491595047246</v>
+        <v>7717.627816495368</v>
       </c>
       <c r="D5">
-        <v>7592.567595047246</v>
+        <v>7639.095816495368</v>
       </c>
       <c r="E5">
-        <v>-2616.524</v>
+        <v>-2531.132</v>
       </c>
       <c r="F5">
-        <v>256.176</v>
+        <v>341.568</v>
       </c>
       <c r="G5">
         <v>420.1</v>
@@ -1703,28 +1703,28 @@
         <v>1520.9</v>
       </c>
       <c r="M5">
-        <v>12.8856528</v>
+        <v>17.1808704</v>
       </c>
       <c r="N5">
-        <v>1508.0143472</v>
+        <v>1503.7191296</v>
       </c>
       <c r="O5">
-        <v>512.7248780479999</v>
+        <v>511.2645040639999</v>
       </c>
       <c r="P5">
-        <v>995.2894691519998</v>
+        <v>992.4546255359996</v>
       </c>
       <c r="Q5">
-        <v>1916.389469152</v>
+        <v>1913.554625536</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09561293212121035</v>
+        <v>0.09595892515852426</v>
       </c>
       <c r="T5">
-        <v>0.6492294935045466</v>
+        <v>0.6537389426537118</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>118.0304966776693</v>
+        <v>88.52287250825195</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09344848815218329</v>
+        <v>0.09315649214679254</v>
       </c>
       <c r="C6">
-        <v>7717.627816495368</v>
+        <v>7679.337815864316</v>
       </c>
       <c r="D6">
-        <v>7639.095816495368</v>
+        <v>7686.197815864316</v>
       </c>
       <c r="E6">
-        <v>-2531.132</v>
+        <v>-2445.74</v>
       </c>
       <c r="F6">
-        <v>341.568</v>
+        <v>426.96</v>
       </c>
       <c r="G6">
         <v>420.1</v>
@@ -1785,28 +1785,28 @@
         <v>1520.9</v>
       </c>
       <c r="M6">
-        <v>17.1808704</v>
+        <v>21.476088</v>
       </c>
       <c r="N6">
-        <v>1503.7191296</v>
+        <v>1499.423912</v>
       </c>
       <c r="O6">
-        <v>511.2645040639999</v>
+        <v>509.8041300799999</v>
       </c>
       <c r="P6">
-        <v>992.4546255359996</v>
+        <v>989.6197819199998</v>
       </c>
       <c r="Q6">
-        <v>1913.554625536</v>
+        <v>1910.71978192</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09595892515852426</v>
+        <v>0.09631220225978163</v>
       </c>
       <c r="T6">
-        <v>0.6537389426537118</v>
+        <v>0.6583433275744384</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>88.52287250825195</v>
+        <v>70.81829800660157</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09315649214679254</v>
+        <v>0.09286449614140181</v>
       </c>
       <c r="C7">
-        <v>7679.337815864316</v>
+        <v>7641.632272596636</v>
       </c>
       <c r="D7">
-        <v>7686.197815864316</v>
+        <v>7733.884272596635</v>
       </c>
       <c r="E7">
-        <v>-2445.74</v>
+        <v>-2360.348</v>
       </c>
       <c r="F7">
-        <v>426.96</v>
+        <v>512.3520000000001</v>
       </c>
       <c r="G7">
         <v>420.1</v>
@@ -1867,28 +1867,28 @@
         <v>1520.9</v>
       </c>
       <c r="M7">
-        <v>21.476088</v>
+        <v>25.7713056</v>
       </c>
       <c r="N7">
-        <v>1499.423912</v>
+        <v>1495.1286944</v>
       </c>
       <c r="O7">
-        <v>509.8041300799999</v>
+        <v>508.3437560959999</v>
       </c>
       <c r="P7">
-        <v>989.6197819199998</v>
+        <v>986.7849383039998</v>
       </c>
       <c r="Q7">
-        <v>1910.71978192</v>
+        <v>1907.884938304</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09631220225978163</v>
+        <v>0.09667299589510832</v>
       </c>
       <c r="T7">
-        <v>0.6583433275744384</v>
+        <v>0.6630456781317763</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>70.81829800660157</v>
+        <v>59.01524833883463</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09286449614140181</v>
+        <v>0.09257250013601107</v>
       </c>
       <c r="C8">
-        <v>7641.632272596636</v>
+        <v>7604.522132817613</v>
       </c>
       <c r="D8">
-        <v>7733.884272596635</v>
+        <v>7782.166132817612</v>
       </c>
       <c r="E8">
-        <v>-2360.348</v>
+        <v>-2274.956</v>
       </c>
       <c r="F8">
-        <v>512.352</v>
+        <v>597.744</v>
       </c>
       <c r="G8">
         <v>420.1</v>
@@ -1949,28 +1949,28 @@
         <v>1520.9</v>
       </c>
       <c r="M8">
-        <v>25.7713056</v>
+        <v>30.0665232</v>
       </c>
       <c r="N8">
-        <v>1495.1286944</v>
+        <v>1490.8334768</v>
       </c>
       <c r="O8">
-        <v>508.3437560959999</v>
+        <v>506.8833821119999</v>
       </c>
       <c r="P8">
-        <v>986.7849383039998</v>
+        <v>983.9500946879998</v>
       </c>
       <c r="Q8">
-        <v>1907.884938304</v>
+        <v>1905.050094688</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09667299589510832</v>
+        <v>0.09704154853334523</v>
       </c>
       <c r="T8">
-        <v>0.6630456781317763</v>
+        <v>0.6678491545075513</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.01524833883464</v>
+        <v>50.58449857614398</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09257250013601107</v>
+        <v>0.09228050413062035</v>
       </c>
       <c r="C9">
-        <v>7604.522132817612</v>
+        <v>7568.018617711921</v>
       </c>
       <c r="D9">
-        <v>7782.166132817612</v>
+        <v>7831.054617711921</v>
       </c>
       <c r="E9">
-        <v>-2274.956</v>
+        <v>-2189.564</v>
       </c>
       <c r="F9">
-        <v>597.7440000000001</v>
+        <v>683.1360000000001</v>
       </c>
       <c r="G9">
         <v>420.1</v>
@@ -2031,28 +2031,28 @@
         <v>1520.9</v>
       </c>
       <c r="M9">
-        <v>30.06652320000001</v>
+        <v>34.3617408</v>
       </c>
       <c r="N9">
-        <v>1490.8334768</v>
+        <v>1486.5382592</v>
       </c>
       <c r="O9">
-        <v>506.8833821119999</v>
+        <v>505.4230081279999</v>
       </c>
       <c r="P9">
-        <v>983.9500946879996</v>
+        <v>981.1152510719996</v>
       </c>
       <c r="Q9">
-        <v>1905.050094687999</v>
+        <v>1902.215251072</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09704154853334525</v>
+        <v>0.0974181131854569</v>
       </c>
       <c r="T9">
-        <v>0.6678491545075514</v>
+        <v>0.6727570542828</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.58449857614396</v>
+        <v>44.26143625412598</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09228050413062035</v>
+        <v>0.0919885081252296</v>
       </c>
       <c r="C10">
-        <v>7568.018617711921</v>
+        <v>7532.133232218042</v>
       </c>
       <c r="D10">
-        <v>7831.054617711921</v>
+        <v>7880.561232218043</v>
       </c>
       <c r="E10">
-        <v>-2189.564</v>
+        <v>-2104.172</v>
       </c>
       <c r="F10">
-        <v>683.1360000000001</v>
+        <v>768.528</v>
       </c>
       <c r="G10">
         <v>420.1</v>
@@ -2113,28 +2113,28 @@
         <v>1520.9</v>
       </c>
       <c r="M10">
-        <v>34.3617408</v>
+        <v>38.6569584</v>
       </c>
       <c r="N10">
-        <v>1486.5382592</v>
+        <v>1482.2430416</v>
       </c>
       <c r="O10">
-        <v>505.4230081279999</v>
+        <v>503.9626341439999</v>
       </c>
       <c r="P10">
-        <v>981.1152510719996</v>
+        <v>978.2804074559998</v>
       </c>
       <c r="Q10">
-        <v>1902.215251072</v>
+        <v>1899.380407456</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0974181131854569</v>
+        <v>0.09780295398376879</v>
       </c>
       <c r="T10">
-        <v>0.6727570542828</v>
+        <v>0.6777728199871749</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.26143625412598</v>
+        <v>39.34349889255643</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0919885081252296</v>
+        <v>0.09169651211983885</v>
       </c>
       <c r="C11">
-        <v>7532.133232218042</v>
+        <v>7496.877774054525</v>
       </c>
       <c r="D11">
-        <v>7880.561232218043</v>
+        <v>7930.697774054524</v>
       </c>
       <c r="E11">
-        <v>-2104.172</v>
+        <v>-2018.78</v>
       </c>
       <c r="F11">
-        <v>768.528</v>
+        <v>853.92</v>
       </c>
       <c r="G11">
         <v>420.1</v>
@@ -2195,28 +2195,28 @@
         <v>1520.9</v>
       </c>
       <c r="M11">
-        <v>38.6569584</v>
+        <v>42.95217599999999</v>
       </c>
       <c r="N11">
-        <v>1482.2430416</v>
+        <v>1477.947824</v>
       </c>
       <c r="O11">
-        <v>503.9626341439999</v>
+        <v>502.5022601599999</v>
       </c>
       <c r="P11">
-        <v>978.2804074559998</v>
+        <v>975.4455638399997</v>
       </c>
       <c r="Q11">
-        <v>1899.380407456</v>
+        <v>1896.54556384</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09780295398376879</v>
+        <v>0.09819634679982095</v>
       </c>
       <c r="T11">
-        <v>0.6777728199871749</v>
+        <v>0.682900047151647</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.34349889255643</v>
+        <v>35.40914900330078</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09169651211983885</v>
+        <v>0.09140451611444812</v>
       </c>
       <c r="C12">
-        <v>7496.877774054525</v>
+        <v>7462.264343093029</v>
       </c>
       <c r="D12">
-        <v>7930.697774054524</v>
+        <v>7981.476343093029</v>
       </c>
       <c r="E12">
-        <v>-2018.78</v>
+        <v>-1933.388</v>
       </c>
       <c r="F12">
-        <v>853.9200000000001</v>
+        <v>939.3120000000001</v>
       </c>
       <c r="G12">
         <v>420.1</v>
@@ -2277,28 +2277,28 @@
         <v>1520.9</v>
       </c>
       <c r="M12">
-        <v>42.952176</v>
+        <v>47.2473936</v>
       </c>
       <c r="N12">
-        <v>1477.947824</v>
+        <v>1473.6526064</v>
       </c>
       <c r="O12">
-        <v>502.5022601599999</v>
+        <v>501.0418861759999</v>
       </c>
       <c r="P12">
-        <v>975.4455638399997</v>
+        <v>972.6107202239998</v>
       </c>
       <c r="Q12">
-        <v>1896.54556384</v>
+        <v>1893.710720224</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09819634679982095</v>
+        <v>0.0985985799038743</v>
       </c>
       <c r="T12">
-        <v>0.682900047151647</v>
+        <v>0.6881424929040848</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.40914900330078</v>
+        <v>32.19013545754616</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09140451611444812</v>
+        <v>0.09111252010905739</v>
       </c>
       <c r="C13">
-        <v>7462.264343093029</v>
+        <v>7428.30535109379</v>
       </c>
       <c r="D13">
-        <v>7981.476343093029</v>
+        <v>8032.909351093789</v>
       </c>
       <c r="E13">
-        <v>-1933.388</v>
+        <v>-1847.996</v>
       </c>
       <c r="F13">
-        <v>939.3120000000001</v>
+        <v>1024.704</v>
       </c>
       <c r="G13">
         <v>420.1</v>
@@ -2359,28 +2359,28 @@
         <v>1520.9</v>
       </c>
       <c r="M13">
-        <v>47.2473936</v>
+        <v>51.5426112</v>
       </c>
       <c r="N13">
-        <v>1473.6526064</v>
+        <v>1469.3573888</v>
       </c>
       <c r="O13">
-        <v>501.0418861759999</v>
+        <v>499.5815121919999</v>
       </c>
       <c r="P13">
-        <v>972.6107202239998</v>
+        <v>969.7758766079996</v>
       </c>
       <c r="Q13">
-        <v>1893.710720224</v>
+        <v>1890.875876608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0985985799038743</v>
+        <v>0.09900995466938339</v>
       </c>
       <c r="T13">
-        <v>0.6881424929040848</v>
+        <v>0.6935040851508962</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.19013545754616</v>
+        <v>29.50762416941732</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09111252010905739</v>
+        <v>0.09082052410366664</v>
       </c>
       <c r="C14">
-        <v>7428.30535109379</v>
+        <v>7395.013531819902</v>
       </c>
       <c r="D14">
-        <v>8032.909351093789</v>
+        <v>8085.009531819903</v>
       </c>
       <c r="E14">
-        <v>-1847.996</v>
+        <v>-1762.604</v>
       </c>
       <c r="F14">
-        <v>1024.704</v>
+        <v>1110.096</v>
       </c>
       <c r="G14">
         <v>420.1</v>
@@ -2441,28 +2441,28 @@
         <v>1520.9</v>
       </c>
       <c r="M14">
-        <v>51.5426112</v>
+        <v>55.83782880000001</v>
       </c>
       <c r="N14">
-        <v>1469.3573888</v>
+        <v>1465.0621712</v>
       </c>
       <c r="O14">
-        <v>499.5815121919999</v>
+        <v>498.1211382079999</v>
       </c>
       <c r="P14">
-        <v>969.7758766079996</v>
+        <v>966.9410329919998</v>
       </c>
       <c r="Q14">
-        <v>1890.875876608</v>
+        <v>1888.041032992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09900995466938339</v>
+        <v>0.09943078632605362</v>
       </c>
       <c r="T14">
-        <v>0.6935040851508962</v>
+        <v>0.6989889323918872</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.50762416941732</v>
+        <v>27.23780692561598</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09082052410366664</v>
+        <v>0.0905285280982759</v>
       </c>
       <c r="C15">
-        <v>7395.013531819902</v>
+        <v>7362.401951547788</v>
       </c>
       <c r="D15">
-        <v>8085.009531819903</v>
+        <v>8137.789951547788</v>
       </c>
       <c r="E15">
-        <v>-1762.604</v>
+        <v>-1677.212</v>
       </c>
       <c r="F15">
-        <v>1110.096</v>
+        <v>1195.488</v>
       </c>
       <c r="G15">
         <v>420.1</v>
@@ -2523,28 +2523,28 @@
         <v>1520.9</v>
       </c>
       <c r="M15">
-        <v>55.83782880000001</v>
+        <v>60.13304640000001</v>
       </c>
       <c r="N15">
-        <v>1465.0621712</v>
+        <v>1460.7669536</v>
       </c>
       <c r="O15">
-        <v>498.1211382079999</v>
+        <v>496.6607642239999</v>
       </c>
       <c r="P15">
-        <v>966.9410329919998</v>
+        <v>964.1061893759997</v>
       </c>
       <c r="Q15">
-        <v>1888.041032992</v>
+        <v>1885.206189376</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09943078632605362</v>
+        <v>0.0998614047654371</v>
       </c>
       <c r="T15">
-        <v>0.6989889323918872</v>
+        <v>0.7046013342198778</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.23780692561598</v>
+        <v>25.29224928807198</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0905285280982759</v>
+        <v>0.09023653209288518</v>
       </c>
       <c r="C16">
-        <v>7362.401951547788</v>
+        <v>7330.484019992052</v>
       </c>
       <c r="D16">
-        <v>8137.789951547788</v>
+        <v>8191.264019992052</v>
       </c>
       <c r="E16">
-        <v>-1677.212</v>
+        <v>-1591.819999999999</v>
       </c>
       <c r="F16">
-        <v>1195.488</v>
+        <v>1280.88</v>
       </c>
       <c r="G16">
         <v>420.1</v>
@@ -2605,28 +2605,28 @@
         <v>1520.9</v>
       </c>
       <c r="M16">
-        <v>60.13304640000001</v>
+        <v>64.42826400000001</v>
       </c>
       <c r="N16">
-        <v>1460.7669536</v>
+        <v>1456.471736</v>
       </c>
       <c r="O16">
-        <v>496.6607642239999</v>
+        <v>495.2003902399999</v>
       </c>
       <c r="P16">
-        <v>964.1061893759997</v>
+        <v>961.2713457599996</v>
       </c>
       <c r="Q16">
-        <v>1885.206189376</v>
+        <v>1882.371345759999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0998614047654371</v>
+        <v>0.1003021554033943</v>
       </c>
       <c r="T16">
-        <v>0.7046013342198778</v>
+        <v>0.7103457925614685</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.29224928807198</v>
+        <v>23.60609933553384</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09023653209288518</v>
+        <v>0.08994453608749442</v>
       </c>
       <c r="C17">
-        <v>7330.484019992052</v>
+        <v>7299.273501663944</v>
       </c>
       <c r="D17">
-        <v>8191.264019992052</v>
+        <v>8245.445501663944</v>
       </c>
       <c r="E17">
-        <v>-1591.82</v>
+        <v>-1506.428</v>
       </c>
       <c r="F17">
-        <v>1280.88</v>
+        <v>1366.272</v>
       </c>
       <c r="G17">
         <v>420.1</v>
@@ -2687,28 +2687,28 @@
         <v>1520.9</v>
       </c>
       <c r="M17">
-        <v>64.428264</v>
+        <v>68.7234816</v>
       </c>
       <c r="N17">
-        <v>1456.471736</v>
+        <v>1452.1765184</v>
       </c>
       <c r="O17">
-        <v>495.2003902399999</v>
+        <v>493.7400162559999</v>
       </c>
       <c r="P17">
-        <v>961.2713457599998</v>
+        <v>958.4365021439996</v>
       </c>
       <c r="Q17">
-        <v>1882.37134576</v>
+        <v>1879.536502144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1003021554033943</v>
+        <v>0.10075340010416</v>
       </c>
       <c r="T17">
-        <v>0.7103457925614685</v>
+        <v>0.7162270237207158</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.60609933553386</v>
+        <v>22.13071812706299</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08994453608749442</v>
+        <v>0.0896525400821037</v>
       </c>
       <c r="C18">
-        <v>7299.273501663944</v>
+        <v>7268.784527683531</v>
       </c>
       <c r="D18">
-        <v>8245.445501663944</v>
+        <v>8300.348527683531</v>
       </c>
       <c r="E18">
-        <v>-1506.428</v>
+        <v>-1421.036</v>
       </c>
       <c r="F18">
-        <v>1366.272</v>
+        <v>1451.664</v>
       </c>
       <c r="G18">
         <v>420.1</v>
@@ -2769,28 +2769,28 @@
         <v>1520.9</v>
       </c>
       <c r="M18">
-        <v>68.7234816</v>
+        <v>73.0186992</v>
       </c>
       <c r="N18">
-        <v>1452.1765184</v>
+        <v>1447.8813008</v>
       </c>
       <c r="O18">
-        <v>493.7400162559999</v>
+        <v>492.2796422719999</v>
       </c>
       <c r="P18">
-        <v>958.4365021439996</v>
+        <v>955.6016585279998</v>
       </c>
       <c r="Q18">
-        <v>1879.536502144</v>
+        <v>1876.701658528</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.10075340010416</v>
+        <v>0.1012155181712093</v>
       </c>
       <c r="T18">
-        <v>0.7162270237207158</v>
+        <v>0.7222499712934392</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.13071812706299</v>
+        <v>20.82891117841222</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0896525400821037</v>
+        <v>0.08936054407671296</v>
       </c>
       <c r="C19">
-        <v>7268.784527683531</v>
+        <v>7239.031608067062</v>
       </c>
       <c r="D19">
-        <v>8300.348527683531</v>
+        <v>8355.987608067062</v>
       </c>
       <c r="E19">
-        <v>-1421.036</v>
+        <v>-1335.644</v>
       </c>
       <c r="F19">
-        <v>1451.664</v>
+        <v>1537.056</v>
       </c>
       <c r="G19">
         <v>420.1</v>
@@ -2851,28 +2851,28 @@
         <v>1520.9</v>
       </c>
       <c r="M19">
-        <v>73.0186992</v>
+        <v>77.31391680000002</v>
       </c>
       <c r="N19">
-        <v>1447.8813008</v>
+        <v>1443.5860832</v>
       </c>
       <c r="O19">
-        <v>492.2796422719999</v>
+        <v>490.8192682879999</v>
       </c>
       <c r="P19">
-        <v>955.6016585279998</v>
+        <v>952.7668149119997</v>
       </c>
       <c r="Q19">
-        <v>1876.701658528</v>
+        <v>1873.866814912</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1012155181712093</v>
+        <v>0.1016889074106256</v>
       </c>
       <c r="T19">
-        <v>0.7222499712934392</v>
+        <v>0.7284198200264727</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.82891117841222</v>
+        <v>19.67174944627821</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08936054407671297</v>
+        <v>0.08906854807132224</v>
       </c>
       <c r="C20">
-        <v>7239.031608067058</v>
+        <v>7210.029644511735</v>
       </c>
       <c r="D20">
-        <v>8355.987608067058</v>
+        <v>8412.377644511735</v>
       </c>
       <c r="E20">
-        <v>-1335.644</v>
+        <v>-1250.252</v>
       </c>
       <c r="F20">
-        <v>1537.056</v>
+        <v>1622.448</v>
       </c>
       <c r="G20">
         <v>420.1</v>
@@ -2933,28 +2933,28 @@
         <v>1520.9</v>
       </c>
       <c r="M20">
-        <v>77.3139168</v>
+        <v>81.6091344</v>
       </c>
       <c r="N20">
-        <v>1443.5860832</v>
+        <v>1439.2908656</v>
       </c>
       <c r="O20">
-        <v>490.8192682879999</v>
+        <v>489.3588943039999</v>
       </c>
       <c r="P20">
-        <v>952.7668149119997</v>
+        <v>949.9319712959998</v>
       </c>
       <c r="Q20">
-        <v>1873.866814912</v>
+        <v>1871.031971296</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1016889074106256</v>
+        <v>0.1021739852732373</v>
       </c>
       <c r="T20">
-        <v>0.7284198200264727</v>
+        <v>0.7347420107035318</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.67174944627821</v>
+        <v>18.63639421226357</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08906854807132224</v>
+        <v>0.08877655206593149</v>
       </c>
       <c r="C21">
-        <v>7210.029644511735</v>
+        <v>7181.793943701754</v>
       </c>
       <c r="D21">
-        <v>8412.377644511735</v>
+        <v>8469.533943701754</v>
       </c>
       <c r="E21">
-        <v>-1250.252</v>
+        <v>-1164.86</v>
       </c>
       <c r="F21">
-        <v>1622.448</v>
+        <v>1707.84</v>
       </c>
       <c r="G21">
         <v>420.1</v>
@@ -3015,28 +3015,28 @@
         <v>1520.9</v>
       </c>
       <c r="M21">
-        <v>81.6091344</v>
+        <v>85.904352</v>
       </c>
       <c r="N21">
-        <v>1439.2908656</v>
+        <v>1434.995648</v>
       </c>
       <c r="O21">
-        <v>489.3588943039999</v>
+        <v>487.8985203199999</v>
       </c>
       <c r="P21">
-        <v>949.9319712959998</v>
+        <v>947.0971276799996</v>
       </c>
       <c r="Q21">
-        <v>1871.031971296</v>
+        <v>1868.19712768</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1021739852732373</v>
+        <v>0.1026711900824144</v>
       </c>
       <c r="T21">
-        <v>0.7347420107035318</v>
+        <v>0.7412222561475175</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.63639421226357</v>
+        <v>17.70457450165039</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08877655206593149</v>
+        <v>0.08848455606054077</v>
       </c>
       <c r="C22">
-        <v>7181.793943701754</v>
+        <v>7154.34023116044</v>
       </c>
       <c r="D22">
-        <v>8469.533943701754</v>
+        <v>8527.47223116044</v>
       </c>
       <c r="E22">
-        <v>-1164.86</v>
+        <v>-1079.467999999999</v>
       </c>
       <c r="F22">
-        <v>1707.84</v>
+        <v>1793.232</v>
       </c>
       <c r="G22">
         <v>420.1</v>
@@ -3097,28 +3097,28 @@
         <v>1520.9</v>
       </c>
       <c r="M22">
-        <v>85.904352</v>
+        <v>90.19956960000002</v>
       </c>
       <c r="N22">
-        <v>1434.995648</v>
+        <v>1430.7004304</v>
       </c>
       <c r="O22">
-        <v>487.8985203199999</v>
+        <v>486.4381463359999</v>
       </c>
       <c r="P22">
-        <v>947.0971276799996</v>
+        <v>944.2622840639998</v>
       </c>
       <c r="Q22">
-        <v>1868.19712768</v>
+        <v>1865.362284064</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1026711900824144</v>
+        <v>0.1031809823551149</v>
       </c>
       <c r="T22">
-        <v>0.7412222561475175</v>
+        <v>0.7478665584381864</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.70457450165039</v>
+        <v>16.86149952538132</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08848455606054076</v>
+        <v>0.08819256005515003</v>
       </c>
       <c r="C23">
-        <v>7154.340231160442</v>
+        <v>7127.684665674895</v>
       </c>
       <c r="D23">
-        <v>8527.472231160442</v>
+        <v>8586.208665674894</v>
       </c>
       <c r="E23">
-        <v>-1079.468</v>
+        <v>-994.0759999999996</v>
       </c>
       <c r="F23">
-        <v>1793.232</v>
+        <v>1878.624</v>
       </c>
       <c r="G23">
         <v>420.1</v>
@@ -3179,28 +3179,28 @@
         <v>1520.9</v>
       </c>
       <c r="M23">
-        <v>90.1995696</v>
+        <v>94.4947872</v>
       </c>
       <c r="N23">
-        <v>1430.7004304</v>
+        <v>1426.4052128</v>
       </c>
       <c r="O23">
-        <v>486.4381463359999</v>
+        <v>484.9777723519999</v>
       </c>
       <c r="P23">
-        <v>944.2622840639998</v>
+        <v>941.4274404479997</v>
       </c>
       <c r="Q23">
-        <v>1865.362284064</v>
+        <v>1862.527440448</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1031809823551149</v>
+        <v>0.1037038462245513</v>
       </c>
       <c r="T23">
-        <v>0.7478665584381862</v>
+        <v>0.7546812274542568</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.86149952538133</v>
+        <v>16.09506772877308</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08819256005515003</v>
+        <v>0.08790056404975928</v>
       </c>
       <c r="C24">
-        <v>7127.684665674895</v>
+        <v>7101.843854320853</v>
       </c>
       <c r="D24">
-        <v>8586.208665674894</v>
+        <v>8645.759854320853</v>
       </c>
       <c r="E24">
-        <v>-994.0759999999996</v>
+        <v>-908.6839999999995</v>
       </c>
       <c r="F24">
-        <v>1878.624</v>
+        <v>1964.016</v>
       </c>
       <c r="G24">
         <v>420.1</v>
@@ -3261,28 +3261,28 @@
         <v>1520.9</v>
       </c>
       <c r="M24">
-        <v>94.4947872</v>
+        <v>98.79000480000001</v>
       </c>
       <c r="N24">
-        <v>1426.4052128</v>
+        <v>1422.1099952</v>
       </c>
       <c r="O24">
-        <v>484.9777723519999</v>
+        <v>483.5173983679999</v>
       </c>
       <c r="P24">
-        <v>941.4274404479997</v>
+        <v>938.5925968319998</v>
       </c>
       <c r="Q24">
-        <v>1862.527440448</v>
+        <v>1859.692596832</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1037038462245513</v>
+        <v>0.1042402909737133</v>
       </c>
       <c r="T24">
-        <v>0.7546812274542568</v>
+        <v>0.7616729008603551</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.09506772877308</v>
+        <v>15.39528217534816</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08790056404975928</v>
+        <v>0.08760856804436856</v>
       </c>
       <c r="C25">
-        <v>7101.843854320853</v>
+        <v>7076.834868117211</v>
       </c>
       <c r="D25">
-        <v>8645.759854320853</v>
+        <v>8706.142868117211</v>
       </c>
       <c r="E25">
-        <v>-908.6839999999995</v>
+        <v>-823.2919999999995</v>
       </c>
       <c r="F25">
-        <v>1964.016</v>
+        <v>2049.408</v>
       </c>
       <c r="G25">
         <v>420.1</v>
@@ -3343,28 +3343,28 @@
         <v>1520.9</v>
       </c>
       <c r="M25">
-        <v>98.79000480000001</v>
+        <v>103.0852224</v>
       </c>
       <c r="N25">
-        <v>1422.1099952</v>
+        <v>1417.8147776</v>
       </c>
       <c r="O25">
-        <v>483.5173983679999</v>
+        <v>482.0570243839999</v>
       </c>
       <c r="P25">
-        <v>938.5925968319998</v>
+        <v>935.7577532159996</v>
       </c>
       <c r="Q25">
-        <v>1859.692596832</v>
+        <v>1856.857753216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1042402909737133</v>
+        <v>0.1047908526899586</v>
       </c>
       <c r="T25">
-        <v>0.7616729008603551</v>
+        <v>0.7688485656718773</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.39528217534816</v>
+        <v>14.75381208470866</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08760856804436853</v>
+        <v>0.08731657203897782</v>
       </c>
       <c r="C26">
-        <v>7076.834868117217</v>
+        <v>7052.675258341161</v>
       </c>
       <c r="D26">
-        <v>8706.142868117216</v>
+        <v>8767.375258341161</v>
       </c>
       <c r="E26">
-        <v>-823.2919999999999</v>
+        <v>-737.8999999999996</v>
       </c>
       <c r="F26">
-        <v>2049.408</v>
+        <v>2134.8</v>
       </c>
       <c r="G26">
         <v>420.1</v>
@@ -3425,28 +3425,28 @@
         <v>1520.9</v>
       </c>
       <c r="M26">
-        <v>103.0852224</v>
+        <v>107.38044</v>
       </c>
       <c r="N26">
-        <v>1417.8147776</v>
+        <v>1413.51956</v>
       </c>
       <c r="O26">
-        <v>482.0570243839999</v>
+        <v>480.5966503999999</v>
       </c>
       <c r="P26">
-        <v>935.7577532159996</v>
+        <v>932.9229095999998</v>
       </c>
       <c r="Q26">
-        <v>1856.857753216</v>
+        <v>1854.0229096</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1047908526899586</v>
+        <v>0.1053560960519704</v>
       </c>
       <c r="T26">
-        <v>0.7688485656718771</v>
+        <v>0.7762155815450398</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.75381208470866</v>
+        <v>14.16365960132031</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08731657203897782</v>
+        <v>0.08702457603358707</v>
       </c>
       <c r="C27">
-        <v>7052.675258341161</v>
+        <v>7029.383073536628</v>
       </c>
       <c r="D27">
-        <v>8767.375258341161</v>
+        <v>8829.475073536629</v>
       </c>
       <c r="E27">
-        <v>-737.8999999999996</v>
+        <v>-652.5079999999994</v>
       </c>
       <c r="F27">
-        <v>2134.8</v>
+        <v>2220.192</v>
       </c>
       <c r="G27">
         <v>420.1</v>
@@ -3507,28 +3507,28 @@
         <v>1520.9</v>
       </c>
       <c r="M27">
-        <v>107.38044</v>
+        <v>111.6756576</v>
       </c>
       <c r="N27">
-        <v>1413.51956</v>
+        <v>1409.2243424</v>
       </c>
       <c r="O27">
-        <v>480.5966503999999</v>
+        <v>479.1362764159999</v>
       </c>
       <c r="P27">
-        <v>932.9229095999998</v>
+        <v>930.0880659839997</v>
       </c>
       <c r="Q27">
-        <v>1854.0229096</v>
+        <v>1851.188065984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1053560960519704</v>
+        <v>0.1059366162616042</v>
       </c>
       <c r="T27">
-        <v>0.7762155815450398</v>
+        <v>0.7837817059553149</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.16365960132031</v>
+        <v>13.61890346280799</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08702457603358707</v>
+        <v>0.08673258002819632</v>
       </c>
       <c r="C28">
-        <v>7029.383073536628</v>
+        <v>7006.976877250781</v>
       </c>
       <c r="D28">
-        <v>8829.475073536629</v>
+        <v>8892.460877250782</v>
       </c>
       <c r="E28">
-        <v>-652.5079999999994</v>
+        <v>-567.1159999999995</v>
       </c>
       <c r="F28">
-        <v>2220.192</v>
+        <v>2305.584</v>
       </c>
       <c r="G28">
         <v>420.1</v>
@@ -3589,28 +3589,28 @@
         <v>1520.9</v>
       </c>
       <c r="M28">
-        <v>111.6756576</v>
+        <v>115.9708752</v>
       </c>
       <c r="N28">
-        <v>1409.2243424</v>
+        <v>1404.9291248</v>
       </c>
       <c r="O28">
-        <v>479.1362764159999</v>
+        <v>477.6759024319999</v>
       </c>
       <c r="P28">
-        <v>930.0880659839997</v>
+        <v>927.2532223679998</v>
       </c>
       <c r="Q28">
-        <v>1851.188065984</v>
+        <v>1848.353222368</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1059366162616042</v>
+        <v>0.1065330411345155</v>
       </c>
       <c r="T28">
-        <v>0.7837817059553149</v>
+        <v>0.7915551214453235</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.61890346280799</v>
+        <v>13.11449963085214</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08673258002819632</v>
+        <v>0.08644058402280559</v>
       </c>
       <c r="C29">
-        <v>7006.976877250781</v>
+        <v>6985.475766535086</v>
       </c>
       <c r="D29">
-        <v>8892.460877250782</v>
+        <v>8956.351766535086</v>
       </c>
       <c r="E29">
-        <v>-567.1159999999995</v>
+        <v>-481.7239999999993</v>
       </c>
       <c r="F29">
-        <v>2305.584</v>
+        <v>2390.976000000001</v>
       </c>
       <c r="G29">
         <v>420.1</v>
@@ -3671,28 +3671,28 @@
         <v>1520.9</v>
       </c>
       <c r="M29">
-        <v>115.9708752</v>
+        <v>120.2660928</v>
       </c>
       <c r="N29">
-        <v>1404.9291248</v>
+        <v>1400.6339072</v>
       </c>
       <c r="O29">
-        <v>477.6759024319999</v>
+        <v>476.2155284479999</v>
       </c>
       <c r="P29">
-        <v>927.2532223679998</v>
+        <v>924.4183787519996</v>
       </c>
       <c r="Q29">
-        <v>1848.353222368</v>
+        <v>1845.518378752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1065330411345155</v>
+        <v>0.1071460333650078</v>
       </c>
       <c r="T29">
-        <v>0.7915551214453235</v>
+        <v>0.799544465143388</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.11449963085214</v>
+        <v>12.64612464403599</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08644058402280559</v>
+        <v>0.08614858801741486</v>
       </c>
       <c r="C30">
-        <v>6985.475766535086</v>
+        <v>6964.89939124973</v>
       </c>
       <c r="D30">
-        <v>8956.351766535086</v>
+        <v>9021.16739124973</v>
       </c>
       <c r="E30">
-        <v>-481.7239999999993</v>
+        <v>-396.3319999999994</v>
       </c>
       <c r="F30">
-        <v>2390.976000000001</v>
+        <v>2476.368</v>
       </c>
       <c r="G30">
         <v>420.1</v>
@@ -3753,28 +3753,28 @@
         <v>1520.9</v>
       </c>
       <c r="M30">
-        <v>120.2660928</v>
+        <v>124.5613104</v>
       </c>
       <c r="N30">
-        <v>1400.6339072</v>
+        <v>1396.3386896</v>
       </c>
       <c r="O30">
-        <v>476.2155284479999</v>
+        <v>474.7551544639999</v>
       </c>
       <c r="P30">
-        <v>924.4183787519996</v>
+        <v>921.5835351359998</v>
       </c>
       <c r="Q30">
-        <v>1845.518378752</v>
+        <v>1842.683535136</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1071460333650078</v>
+        <v>0.1077762929822745</v>
       </c>
       <c r="T30">
-        <v>0.799544465143388</v>
+        <v>0.8077588607766092</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.64612464403599</v>
+        <v>12.21005138044854</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08614858801741486</v>
+        <v>0.08585659201202411</v>
       </c>
       <c r="C31">
-        <v>6964.89939124973</v>
+        <v>6945.267974212342</v>
       </c>
       <c r="D31">
-        <v>9021.16739124973</v>
+        <v>9086.927974212342</v>
       </c>
       <c r="E31">
-        <v>-396.3319999999999</v>
+        <v>-310.9399999999996</v>
       </c>
       <c r="F31">
-        <v>2476.368</v>
+        <v>2561.76</v>
       </c>
       <c r="G31">
         <v>420.1</v>
@@ -3835,28 +3835,28 @@
         <v>1520.9</v>
       </c>
       <c r="M31">
-        <v>124.5613104</v>
+        <v>128.856528</v>
       </c>
       <c r="N31">
-        <v>1396.3386896</v>
+        <v>1392.043472</v>
       </c>
       <c r="O31">
-        <v>474.7551544639999</v>
+        <v>473.2947804799999</v>
       </c>
       <c r="P31">
-        <v>921.5835351359998</v>
+        <v>918.7486915199997</v>
       </c>
       <c r="Q31">
-        <v>1842.683535136</v>
+        <v>1839.84869152</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1077762929822745</v>
+        <v>0.1084245600171773</v>
       </c>
       <c r="T31">
-        <v>0.8077588607766092</v>
+        <v>0.8162079534279224</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.21005138044855</v>
+        <v>11.80304966776693</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08585659201202411</v>
+        <v>0.08556459600663338</v>
       </c>
       <c r="C32">
-        <v>6945.267974212342</v>
+        <v>6926.602332234454</v>
       </c>
       <c r="D32">
-        <v>9086.927974212342</v>
+        <v>9153.654332234453</v>
       </c>
       <c r="E32">
-        <v>-310.9399999999996</v>
+        <v>-225.5479999999998</v>
       </c>
       <c r="F32">
-        <v>2561.76</v>
+        <v>2647.152</v>
       </c>
       <c r="G32">
         <v>420.1</v>
@@ -3917,28 +3917,28 @@
         <v>1520.9</v>
       </c>
       <c r="M32">
-        <v>128.856528</v>
+        <v>133.1517456</v>
       </c>
       <c r="N32">
-        <v>1392.043472</v>
+        <v>1387.7482544</v>
       </c>
       <c r="O32">
-        <v>473.2947804799999</v>
+        <v>471.8344064959999</v>
       </c>
       <c r="P32">
-        <v>918.7486915199997</v>
+        <v>915.9138479039998</v>
       </c>
       <c r="Q32">
-        <v>1839.84869152</v>
+        <v>1837.013847904</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1084245600171773</v>
+        <v>0.1090916174009179</v>
       </c>
       <c r="T32">
-        <v>0.8162079534279224</v>
+        <v>0.8249019473155056</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.80304966776693</v>
+        <v>11.42230613009703</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08556459600663338</v>
+        <v>0.08527260000124263</v>
       </c>
       <c r="C33">
-        <v>6926.602332234454</v>
+        <v>6908.923898091682</v>
       </c>
       <c r="D33">
-        <v>9153.654332234453</v>
+        <v>9221.367898091681</v>
       </c>
       <c r="E33">
-        <v>-225.5479999999998</v>
+        <v>-140.1559999999995</v>
       </c>
       <c r="F33">
-        <v>2647.152</v>
+        <v>2732.544</v>
       </c>
       <c r="G33">
         <v>420.1</v>
@@ -3999,28 +3999,28 @@
         <v>1520.9</v>
       </c>
       <c r="M33">
-        <v>133.1517456</v>
+        <v>137.4469632</v>
       </c>
       <c r="N33">
-        <v>1387.7482544</v>
+        <v>1383.4530368</v>
       </c>
       <c r="O33">
-        <v>471.8344064959999</v>
+        <v>470.3740325119999</v>
       </c>
       <c r="P33">
-        <v>915.9138479039998</v>
+        <v>913.0790042879996</v>
       </c>
       <c r="Q33">
-        <v>1837.013847904</v>
+        <v>1834.179004288</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1090916174009179</v>
+        <v>0.1097782941194745</v>
       </c>
       <c r="T33">
-        <v>0.8249019473155056</v>
+        <v>0.8338516469056647</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.42230613009703</v>
+        <v>11.06535906353149</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08527260000124263</v>
+        <v>0.0849806039958519</v>
       </c>
       <c r="C34">
-        <v>6908.923898091682</v>
+        <v>6892.254743476255</v>
       </c>
       <c r="D34">
-        <v>9221.367898091681</v>
+        <v>9290.090743476254</v>
       </c>
       <c r="E34">
-        <v>-140.1559999999995</v>
+        <v>-54.76399999999967</v>
       </c>
       <c r="F34">
-        <v>2732.544</v>
+        <v>2817.936</v>
       </c>
       <c r="G34">
         <v>420.1</v>
@@ -4081,28 +4081,28 @@
         <v>1520.9</v>
       </c>
       <c r="M34">
-        <v>137.4469632</v>
+        <v>141.7421808</v>
       </c>
       <c r="N34">
-        <v>1383.4530368</v>
+        <v>1379.1578192</v>
       </c>
       <c r="O34">
-        <v>470.3740325119999</v>
+        <v>468.9136585279999</v>
       </c>
       <c r="P34">
-        <v>913.0790042879996</v>
+        <v>910.2441606719998</v>
       </c>
       <c r="Q34">
-        <v>1834.179004288</v>
+        <v>1831.344160672</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1097782941194745</v>
+        <v>0.1104854686505252</v>
       </c>
       <c r="T34">
-        <v>0.8338516469056647</v>
+        <v>0.8430685017074704</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.06535906353149</v>
+        <v>10.73004515251539</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0849806039958519</v>
+        <v>0.08468860799046117</v>
       </c>
       <c r="C35">
-        <v>6892.254743476255</v>
+        <v>6876.617602983642</v>
       </c>
       <c r="D35">
-        <v>9290.090743476254</v>
+        <v>9359.845602983642</v>
       </c>
       <c r="E35">
-        <v>-54.76399999999967</v>
+        <v>30.62800000000061</v>
       </c>
       <c r="F35">
-        <v>2817.936</v>
+        <v>2903.328</v>
       </c>
       <c r="G35">
         <v>420.1</v>
@@ -4163,28 +4163,28 @@
         <v>1520.9</v>
       </c>
       <c r="M35">
-        <v>141.7421808</v>
+        <v>146.0373984</v>
       </c>
       <c r="N35">
-        <v>1379.1578192</v>
+        <v>1374.8626016</v>
       </c>
       <c r="O35">
-        <v>468.9136585279999</v>
+        <v>467.4532845439999</v>
       </c>
       <c r="P35">
-        <v>910.2441606719998</v>
+        <v>907.4093170559997</v>
       </c>
       <c r="Q35">
-        <v>1831.344160672</v>
+        <v>1828.509317056</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1104854686505252</v>
+        <v>0.11121407271282</v>
       </c>
       <c r="T35">
-        <v>0.8430685017074704</v>
+        <v>0.8525646551396339</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.73004515251539</v>
+        <v>10.41445558920611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08468860799046117</v>
+        <v>0.08439661198507041</v>
       </c>
       <c r="C36">
-        <v>6876.617602983642</v>
+        <v>6862.035899187948</v>
       </c>
       <c r="D36">
-        <v>9359.845602983642</v>
+        <v>9430.655899187948</v>
       </c>
       <c r="E36">
-        <v>30.62800000000061</v>
+        <v>116.0200000000009</v>
       </c>
       <c r="F36">
-        <v>2903.328</v>
+        <v>2988.720000000001</v>
       </c>
       <c r="G36">
         <v>420.1</v>
@@ -4245,28 +4245,28 @@
         <v>1520.9</v>
       </c>
       <c r="M36">
-        <v>146.0373984</v>
+        <v>150.332616</v>
       </c>
       <c r="N36">
-        <v>1374.8626016</v>
+        <v>1370.567383999999</v>
       </c>
       <c r="O36">
-        <v>467.4532845439999</v>
+        <v>465.9929105599999</v>
       </c>
       <c r="P36">
-        <v>907.4093170559997</v>
+        <v>904.5744734399996</v>
       </c>
       <c r="Q36">
-        <v>1828.509317056</v>
+        <v>1825.674473439999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.11121407271282</v>
+        <v>0.1119650953616468</v>
       </c>
       <c r="T36">
-        <v>0.8525646551396339</v>
+        <v>0.8623529979081715</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.41445558920611</v>
+        <v>10.11689971522879</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08439661198507041</v>
+        <v>0.08410461597967968</v>
       </c>
       <c r="C37">
-        <v>6862.035899187948</v>
+        <v>6848.533768864181</v>
       </c>
       <c r="D37">
-        <v>9430.655899187948</v>
+        <v>9502.545768864182</v>
       </c>
       <c r="E37">
-        <v>116.0200000000009</v>
+        <v>201.4120000000007</v>
       </c>
       <c r="F37">
-        <v>2988.720000000001</v>
+        <v>3074.112000000001</v>
       </c>
       <c r="G37">
         <v>420.1</v>
@@ -4327,28 +4327,28 @@
         <v>1520.9</v>
       </c>
       <c r="M37">
-        <v>150.332616</v>
+        <v>154.6278336</v>
       </c>
       <c r="N37">
-        <v>1370.567383999999</v>
+        <v>1366.2721664</v>
       </c>
       <c r="O37">
-        <v>465.9929105599999</v>
+        <v>464.5325365759999</v>
       </c>
       <c r="P37">
-        <v>904.5744734399996</v>
+        <v>901.7396298239996</v>
       </c>
       <c r="Q37">
-        <v>1825.674473439999</v>
+        <v>1822.839629824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1119650953616468</v>
+        <v>0.1127395874682495</v>
       </c>
       <c r="T37">
-        <v>0.8623529979081715</v>
+        <v>0.8724472263882261</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.11689971522879</v>
+        <v>9.835874723139103</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08410461597967969</v>
+        <v>0.08381261997428896</v>
       </c>
       <c r="C38">
-        <v>6848.533768864178</v>
+        <v>6836.13609041917</v>
       </c>
       <c r="D38">
-        <v>9502.545768864178</v>
+        <v>9575.54009041917</v>
       </c>
       <c r="E38">
-        <v>201.4120000000003</v>
+        <v>286.8040000000005</v>
       </c>
       <c r="F38">
-        <v>3074.112</v>
+        <v>3159.504</v>
       </c>
       <c r="G38">
         <v>420.1</v>
@@ -4409,28 +4409,28 @@
         <v>1520.9</v>
       </c>
       <c r="M38">
-        <v>154.6278336</v>
+        <v>158.9230512</v>
       </c>
       <c r="N38">
-        <v>1366.2721664</v>
+        <v>1361.9769488</v>
       </c>
       <c r="O38">
-        <v>464.5325365759999</v>
+        <v>463.0721625919999</v>
       </c>
       <c r="P38">
-        <v>901.7396298239996</v>
+        <v>898.9047862079998</v>
       </c>
       <c r="Q38">
-        <v>1822.839629824</v>
+        <v>1820.004786208</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1127395874682495</v>
+        <v>0.1135386666258555</v>
       </c>
       <c r="T38">
-        <v>0.872447226388226</v>
+        <v>0.88286190656606</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.835874723139105</v>
+        <v>9.570040271162373</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08381261997428896</v>
+        <v>0.08352062396889823</v>
       </c>
       <c r="C39">
-        <v>6836.13609041917</v>
+        <v>6824.868512596455</v>
       </c>
       <c r="D39">
-        <v>9575.54009041917</v>
+        <v>9649.664512596455</v>
       </c>
       <c r="E39">
-        <v>286.8040000000005</v>
+        <v>372.1960000000004</v>
       </c>
       <c r="F39">
-        <v>3159.504</v>
+        <v>3244.896</v>
       </c>
       <c r="G39">
         <v>420.1</v>
@@ -4491,28 +4491,28 @@
         <v>1520.9</v>
       </c>
       <c r="M39">
-        <v>158.9230512</v>
+        <v>163.2182688</v>
       </c>
       <c r="N39">
-        <v>1361.9769488</v>
+        <v>1357.6817312</v>
       </c>
       <c r="O39">
-        <v>463.0721625919999</v>
+        <v>461.6117886079999</v>
       </c>
       <c r="P39">
-        <v>898.9047862079998</v>
+        <v>896.0699425919997</v>
       </c>
       <c r="Q39">
-        <v>1820.004786208</v>
+        <v>1817.169942592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1135386666258555</v>
+        <v>0.114363522530481</v>
       </c>
       <c r="T39">
-        <v>0.88286190656606</v>
+        <v>0.8936125441689855</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.570040271162373</v>
+        <v>9.318197106131784</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08352062396889823</v>
+        <v>0.08322862796350748</v>
       </c>
       <c r="C40">
-        <v>6824.868512596455</v>
+        <v>6814.757484524845</v>
       </c>
       <c r="D40">
-        <v>9649.664512596455</v>
+        <v>9724.945484524846</v>
       </c>
       <c r="E40">
-        <v>372.1960000000004</v>
+        <v>457.5880000000006</v>
       </c>
       <c r="F40">
-        <v>3244.896</v>
+        <v>3330.288</v>
       </c>
       <c r="G40">
         <v>420.1</v>
@@ -4573,28 +4573,28 @@
         <v>1520.9</v>
       </c>
       <c r="M40">
-        <v>163.2182688</v>
+        <v>167.5134864</v>
       </c>
       <c r="N40">
-        <v>1357.6817312</v>
+        <v>1353.3865136</v>
       </c>
       <c r="O40">
-        <v>461.6117886079999</v>
+        <v>460.1514146239999</v>
       </c>
       <c r="P40">
-        <v>896.0699425919997</v>
+        <v>893.2350989759998</v>
       </c>
       <c r="Q40">
-        <v>1817.169942592</v>
+        <v>1814.335098976</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.114363522530481</v>
+        <v>0.1152154228909959</v>
       </c>
       <c r="T40">
-        <v>0.8936125441689855</v>
+        <v>0.9047156616933183</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.318197106131784</v>
+        <v>9.079268975205329</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08322862796350748</v>
+        <v>0.08293663195811674</v>
       </c>
       <c r="C41">
-        <v>6814.757484524845</v>
+        <v>6805.830287184566</v>
       </c>
       <c r="D41">
-        <v>9724.945484524846</v>
+        <v>9801.410287184566</v>
       </c>
       <c r="E41">
-        <v>457.5880000000006</v>
+        <v>542.9800000000005</v>
       </c>
       <c r="F41">
-        <v>3330.288</v>
+        <v>3415.68</v>
       </c>
       <c r="G41">
         <v>420.1</v>
@@ -4655,28 +4655,28 @@
         <v>1520.9</v>
       </c>
       <c r="M41">
-        <v>167.5134864</v>
+        <v>171.808704</v>
       </c>
       <c r="N41">
-        <v>1353.3865136</v>
+        <v>1349.091296</v>
       </c>
       <c r="O41">
-        <v>460.1514146239999</v>
+        <v>458.6910406399999</v>
       </c>
       <c r="P41">
-        <v>893.2350989759998</v>
+        <v>890.4002553599997</v>
       </c>
       <c r="Q41">
-        <v>1814.335098976</v>
+        <v>1811.50025536</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1152154228909959</v>
+        <v>0.1160957199301946</v>
       </c>
       <c r="T41">
-        <v>0.9047156616933183</v>
+        <v>0.9161888831351289</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.079268975205329</v>
+        <v>8.852287250825194</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08293663195811674</v>
+        <v>0.08305053595272602</v>
       </c>
       <c r="C42">
-        <v>6805.830287184566</v>
+        <v>6690.46771747433</v>
       </c>
       <c r="D42">
-        <v>9801.410287184566</v>
+        <v>9771.43971747433</v>
       </c>
       <c r="E42">
-        <v>542.9800000000005</v>
+        <v>628.3720000000008</v>
       </c>
       <c r="F42">
-        <v>3415.68</v>
+        <v>3501.072000000001</v>
       </c>
       <c r="G42">
         <v>420.1</v>
@@ -4737,45 +4737,45 @@
         <v>1520.9</v>
       </c>
       <c r="M42">
-        <v>171.808704</v>
+        <v>181.3555296</v>
       </c>
       <c r="N42">
-        <v>1349.091296</v>
+        <v>1339.5444704</v>
       </c>
       <c r="O42">
-        <v>458.6910406399999</v>
+        <v>455.4451199359999</v>
       </c>
       <c r="P42">
-        <v>890.4002553599997</v>
+        <v>884.0993504639998</v>
       </c>
       <c r="Q42">
-        <v>1811.50025536</v>
+        <v>1805.199350464</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1160957199301946</v>
+        <v>0.1170058575469932</v>
       </c>
       <c r="T42">
-        <v>0.9161888831351289</v>
+        <v>0.9280510273376789</v>
       </c>
       <c r="U42">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V42">
         <v>0.34</v>
       </c>
       <c r="W42">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y42">
-        <v>8.852287250825194</v>
+        <v>8.386289645286887</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08305053595272602</v>
+        <v>0.08276843994733526</v>
       </c>
       <c r="C43">
-        <v>6690.46771747433</v>
+        <v>6679.638888523551</v>
       </c>
       <c r="D43">
-        <v>9771.43971747433</v>
+        <v>9846.002888523552</v>
       </c>
       <c r="E43">
-        <v>628.3720000000008</v>
+        <v>713.764000000001</v>
       </c>
       <c r="F43">
-        <v>3501.072000000001</v>
+        <v>3586.464000000001</v>
       </c>
       <c r="G43">
         <v>420.1</v>
@@ -4819,28 +4819,28 @@
         <v>1520.9</v>
       </c>
       <c r="M43">
-        <v>181.3555296</v>
+        <v>185.7788352</v>
       </c>
       <c r="N43">
-        <v>1339.5444704</v>
+        <v>1335.1211648</v>
       </c>
       <c r="O43">
-        <v>455.4451199359999</v>
+        <v>453.9411960319999</v>
       </c>
       <c r="P43">
-        <v>884.0993504639998</v>
+        <v>881.1799687679998</v>
       </c>
       <c r="Q43">
-        <v>1805.199350464</v>
+        <v>1802.279968768</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1170058575469932</v>
+        <v>0.1179473792195436</v>
       </c>
       <c r="T43">
-        <v>0.9280510273376789</v>
+        <v>0.9403222109954892</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.386289645286887</v>
+        <v>8.186616082303864</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08276843994733526</v>
+        <v>0.08248634394194453</v>
       </c>
       <c r="C44">
-        <v>6679.638888523552</v>
+        <v>6669.956751798933</v>
       </c>
       <c r="D44">
-        <v>9846.002888523552</v>
+        <v>9921.712751798932</v>
       </c>
       <c r="E44">
-        <v>713.7640000000006</v>
+        <v>799.1560000000004</v>
       </c>
       <c r="F44">
-        <v>3586.464</v>
+        <v>3671.856</v>
       </c>
       <c r="G44">
         <v>420.1</v>
@@ -4901,28 +4901,28 @@
         <v>1520.9</v>
       </c>
       <c r="M44">
-        <v>185.7788352</v>
+        <v>190.2021408</v>
       </c>
       <c r="N44">
-        <v>1335.1211648</v>
+        <v>1330.6978592</v>
       </c>
       <c r="O44">
-        <v>453.9411960319999</v>
+        <v>452.4372721279999</v>
       </c>
       <c r="P44">
-        <v>881.1799687679998</v>
+        <v>878.2605870719997</v>
       </c>
       <c r="Q44">
-        <v>1802.279968768</v>
+        <v>1799.360587072</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1179473792195436</v>
+        <v>0.1189219367402536</v>
       </c>
       <c r="T44">
-        <v>0.9403222109954891</v>
+        <v>0.9530239625009418</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.186616082303866</v>
+        <v>7.996229661785172</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08248634394194453</v>
+        <v>0.0822042479365538</v>
       </c>
       <c r="C45">
-        <v>6669.956751798933</v>
+        <v>6661.44796440628</v>
       </c>
       <c r="D45">
-        <v>9921.712751798932</v>
+        <v>9998.59596440628</v>
       </c>
       <c r="E45">
-        <v>799.1560000000004</v>
+        <v>884.5480000000007</v>
       </c>
       <c r="F45">
-        <v>3671.856</v>
+        <v>3757.248000000001</v>
       </c>
       <c r="G45">
         <v>420.1</v>
@@ -4983,28 +4983,28 @@
         <v>1520.9</v>
       </c>
       <c r="M45">
-        <v>190.2021408</v>
+        <v>194.6254464</v>
       </c>
       <c r="N45">
-        <v>1330.6978592</v>
+        <v>1326.2745536</v>
       </c>
       <c r="O45">
-        <v>452.4372721279999</v>
+        <v>450.9333482239999</v>
       </c>
       <c r="P45">
-        <v>878.2605870719997</v>
+        <v>875.3412053759996</v>
       </c>
       <c r="Q45">
-        <v>1799.360587072</v>
+        <v>1796.441205376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1189219367402536</v>
+        <v>0.1199312998867032</v>
       </c>
       <c r="T45">
-        <v>0.9530239625009418</v>
+        <v>0.9661793479887321</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.996229661785172</v>
+        <v>7.814497169471871</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0822042479365538</v>
+        <v>0.08192215193116306</v>
       </c>
       <c r="C46">
-        <v>6661.44796440628</v>
+        <v>6654.140016166267</v>
       </c>
       <c r="D46">
-        <v>9998.59596440628</v>
+        <v>10076.68001616627</v>
       </c>
       <c r="E46">
-        <v>884.5480000000007</v>
+        <v>969.9400000000005</v>
       </c>
       <c r="F46">
-        <v>3757.248000000001</v>
+        <v>3842.64</v>
       </c>
       <c r="G46">
         <v>420.1</v>
@@ -5065,28 +5065,28 @@
         <v>1520.9</v>
       </c>
       <c r="M46">
-        <v>194.6254464</v>
+        <v>199.048752</v>
       </c>
       <c r="N46">
-        <v>1326.2745536</v>
+        <v>1321.851248</v>
       </c>
       <c r="O46">
-        <v>450.9333482239999</v>
+        <v>449.42942432</v>
       </c>
       <c r="P46">
-        <v>875.3412053759996</v>
+        <v>872.4218236799998</v>
       </c>
       <c r="Q46">
-        <v>1796.441205376</v>
+        <v>1793.52182368</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1199312998867032</v>
+        <v>0.1209773671475692</v>
       </c>
       <c r="T46">
-        <v>0.9661793479887321</v>
+        <v>0.979813111130624</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.814497169471871</v>
+        <v>7.640841676816942</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08192215193116306</v>
+        <v>0.08164005592577234</v>
       </c>
       <c r="C47">
-        <v>6654.140016166267</v>
+        <v>6648.061262385754</v>
       </c>
       <c r="D47">
-        <v>10076.68001616627</v>
+        <v>10155.99326238575</v>
       </c>
       <c r="E47">
-        <v>969.9400000000005</v>
+        <v>1055.332000000001</v>
       </c>
       <c r="F47">
-        <v>3842.64</v>
+        <v>3928.032000000001</v>
       </c>
       <c r="G47">
         <v>420.1</v>
@@ -5147,28 +5147,28 @@
         <v>1520.9</v>
       </c>
       <c r="M47">
-        <v>199.048752</v>
+        <v>203.4720576</v>
       </c>
       <c r="N47">
-        <v>1321.851248</v>
+        <v>1317.4279424</v>
       </c>
       <c r="O47">
-        <v>449.42942432</v>
+        <v>447.9255004159999</v>
       </c>
       <c r="P47">
-        <v>872.4218236799998</v>
+        <v>869.5024419839997</v>
       </c>
       <c r="Q47">
-        <v>1793.52182368</v>
+        <v>1790.602441984</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1209773671475692</v>
+        <v>0.1220621776403191</v>
       </c>
       <c r="T47">
-        <v>0.979813111130624</v>
+        <v>0.9939518284629562</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.640841676816942</v>
+        <v>7.474736422973095</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08164005592577234</v>
+        <v>0.0813579599203816</v>
       </c>
       <c r="C48">
-        <v>6648.061262385754</v>
+        <v>6643.24095818915</v>
       </c>
       <c r="D48">
-        <v>10155.99326238575</v>
+        <v>10236.56495818915</v>
       </c>
       <c r="E48">
-        <v>1055.332000000001</v>
+        <v>1140.724000000001</v>
       </c>
       <c r="F48">
-        <v>3928.032000000001</v>
+        <v>4013.424</v>
       </c>
       <c r="G48">
         <v>420.1</v>
@@ -5229,28 +5229,28 @@
         <v>1520.9</v>
       </c>
       <c r="M48">
-        <v>203.4720576</v>
+        <v>207.8953632</v>
       </c>
       <c r="N48">
-        <v>1317.4279424</v>
+        <v>1313.0046368</v>
       </c>
       <c r="O48">
-        <v>447.9255004159999</v>
+        <v>446.4215765119999</v>
       </c>
       <c r="P48">
-        <v>869.5024419839997</v>
+        <v>866.5830602879997</v>
       </c>
       <c r="Q48">
-        <v>1790.602441984</v>
+        <v>1787.683060288</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1220621776403191</v>
+        <v>0.1231879243780785</v>
       </c>
       <c r="T48">
-        <v>0.9939518284629562</v>
+        <v>1.008624082298395</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.474736422973095</v>
+        <v>7.315699477803454</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0813579599203816</v>
+        <v>0.08107586391499086</v>
       </c>
       <c r="C49">
-        <v>6643.24095818915</v>
+        <v>6639.70929449691</v>
       </c>
       <c r="D49">
-        <v>10236.56495818915</v>
+        <v>10318.42529449691</v>
       </c>
       <c r="E49">
-        <v>1140.724000000001</v>
+        <v>1226.116000000001</v>
       </c>
       <c r="F49">
-        <v>4013.424</v>
+        <v>4098.816000000001</v>
       </c>
       <c r="G49">
         <v>420.1</v>
@@ -5311,28 +5311,28 @@
         <v>1520.9</v>
       </c>
       <c r="M49">
-        <v>207.8953632</v>
+        <v>212.3186688</v>
       </c>
       <c r="N49">
-        <v>1313.0046368</v>
+        <v>1308.5813312</v>
       </c>
       <c r="O49">
-        <v>446.4215765119999</v>
+        <v>444.9176526079999</v>
       </c>
       <c r="P49">
-        <v>866.5830602879997</v>
+        <v>863.6636785919997</v>
       </c>
       <c r="Q49">
-        <v>1787.683060288</v>
+        <v>1784.763678591999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1231879243780785</v>
+        <v>0.1243569690672901</v>
       </c>
       <c r="T49">
-        <v>1.008624082298395</v>
+        <v>1.023860653589044</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.315699477803454</v>
+        <v>7.163289072015882</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08107586391499084</v>
+        <v>0.08079376790960011</v>
       </c>
       <c r="C50">
-        <v>6639.709294496914</v>
+        <v>6637.497435744344</v>
       </c>
       <c r="D50">
-        <v>10318.42529449691</v>
+        <v>10401.60543574434</v>
       </c>
       <c r="E50">
-        <v>1226.116</v>
+        <v>1311.508000000001</v>
       </c>
       <c r="F50">
-        <v>4098.816</v>
+        <v>4184.208000000001</v>
       </c>
       <c r="G50">
         <v>420.1</v>
@@ -5393,28 +5393,28 @@
         <v>1520.9</v>
       </c>
       <c r="M50">
-        <v>212.3186688</v>
+        <v>216.7419744</v>
       </c>
       <c r="N50">
-        <v>1308.5813312</v>
+        <v>1304.1580256</v>
       </c>
       <c r="O50">
-        <v>444.9176526079999</v>
+        <v>443.4137287039999</v>
       </c>
       <c r="P50">
-        <v>863.6636785919997</v>
+        <v>860.7442968959997</v>
       </c>
       <c r="Q50">
-        <v>1784.763678591999</v>
+        <v>1781.844296896</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1243569690672901</v>
+        <v>0.1255718586462747</v>
       </c>
       <c r="T50">
-        <v>1.023860653589044</v>
+        <v>1.039694737479325</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.163289072015884</v>
+        <v>7.017099499117599</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08079376790960011</v>
+        <v>0.08051167190420938</v>
       </c>
       <c r="C51">
-        <v>6637.497435744344</v>
+        <v>6636.637559439549</v>
       </c>
       <c r="D51">
-        <v>10401.60543574434</v>
+        <v>10486.13755943955</v>
       </c>
       <c r="E51">
-        <v>1311.508000000001</v>
+        <v>1396.900000000001</v>
       </c>
       <c r="F51">
-        <v>4184.208000000001</v>
+        <v>4269.6</v>
       </c>
       <c r="G51">
         <v>420.1</v>
@@ -5475,28 +5475,28 @@
         <v>1520.9</v>
       </c>
       <c r="M51">
-        <v>216.7419744</v>
+        <v>221.16528</v>
       </c>
       <c r="N51">
-        <v>1304.1580256</v>
+        <v>1299.73472</v>
       </c>
       <c r="O51">
-        <v>443.4137287039999</v>
+        <v>441.9098047999999</v>
       </c>
       <c r="P51">
-        <v>860.7442968959997</v>
+        <v>857.8249151999999</v>
       </c>
       <c r="Q51">
-        <v>1781.844296896</v>
+        <v>1778.9249152</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1255718586462747</v>
+        <v>0.1268353438084188</v>
       </c>
       <c r="T51">
-        <v>1.039694737479325</v>
+        <v>1.056162184725218</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.017099499117599</v>
+        <v>6.876757509135247</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08051167190420938</v>
+        <v>0.08022957589881864</v>
       </c>
       <c r="C52">
-        <v>6636.637559439549</v>
+        <v>6637.162897666105</v>
       </c>
       <c r="D52">
-        <v>10486.13755943955</v>
+        <v>10572.0548976661</v>
       </c>
       <c r="E52">
-        <v>1396.900000000001</v>
+        <v>1482.292</v>
       </c>
       <c r="F52">
-        <v>4269.6</v>
+        <v>4354.992</v>
       </c>
       <c r="G52">
         <v>420.1</v>
@@ -5557,28 +5557,28 @@
         <v>1520.9</v>
       </c>
       <c r="M52">
-        <v>221.16528</v>
+        <v>225.5885856</v>
       </c>
       <c r="N52">
-        <v>1299.73472</v>
+        <v>1295.3114144</v>
       </c>
       <c r="O52">
-        <v>441.9098047999999</v>
+        <v>440.4058808959999</v>
       </c>
       <c r="P52">
-        <v>857.8249151999999</v>
+        <v>854.9055335039998</v>
       </c>
       <c r="Q52">
-        <v>1778.9249152</v>
+        <v>1776.005533504</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1268353438084188</v>
+        <v>0.1281503997935074</v>
       </c>
       <c r="T52">
-        <v>1.056162184725218</v>
+        <v>1.073301772675025</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.876757509135247</v>
+        <v>6.741919126603184</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08022957589881864</v>
+        <v>0.08053091989342789</v>
       </c>
       <c r="C53">
-        <v>6637.162897666105</v>
+        <v>6460.042107761698</v>
       </c>
       <c r="D53">
-        <v>10572.0548976661</v>
+        <v>10480.3261077617</v>
       </c>
       <c r="E53">
-        <v>1482.292</v>
+        <v>1567.684000000001</v>
       </c>
       <c r="F53">
-        <v>4354.992</v>
+        <v>4440.384000000001</v>
       </c>
       <c r="G53">
         <v>420.1</v>
@@ -5639,45 +5639,45 @@
         <v>1520.9</v>
       </c>
       <c r="M53">
-        <v>225.5885856</v>
+        <v>237.560544</v>
       </c>
       <c r="N53">
-        <v>1295.3114144</v>
+        <v>1283.339456</v>
       </c>
       <c r="O53">
-        <v>440.4058808959999</v>
+        <v>436.3354150399999</v>
       </c>
       <c r="P53">
-        <v>854.9055335039998</v>
+        <v>847.0040409599998</v>
       </c>
       <c r="Q53">
-        <v>1776.005533504</v>
+        <v>1768.10404096</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1281503997935074</v>
+        <v>0.1295202497779748</v>
       </c>
       <c r="T53">
-        <v>1.073301772675025</v>
+        <v>1.09115551012274</v>
       </c>
       <c r="U53">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V53">
         <v>0.34</v>
       </c>
       <c r="W53">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.741919126603184</v>
+        <v>6.402157422235906</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08053091989342789</v>
+        <v>0.08026004388803716</v>
       </c>
       <c r="C54">
-        <v>6460.042107761698</v>
+        <v>6457.031571943414</v>
       </c>
       <c r="D54">
-        <v>10480.3261077617</v>
+        <v>10562.70757194341</v>
       </c>
       <c r="E54">
-        <v>1567.684000000001</v>
+        <v>1653.076000000001</v>
       </c>
       <c r="F54">
-        <v>4440.384000000001</v>
+        <v>4525.776000000001</v>
       </c>
       <c r="G54">
         <v>420.1</v>
@@ -5721,28 +5721,28 @@
         <v>1520.9</v>
       </c>
       <c r="M54">
-        <v>237.560544</v>
+        <v>242.129016</v>
       </c>
       <c r="N54">
-        <v>1283.339456</v>
+        <v>1278.770984</v>
       </c>
       <c r="O54">
-        <v>436.3354150399999</v>
+        <v>434.7821345599999</v>
       </c>
       <c r="P54">
-        <v>847.0040409599998</v>
+        <v>843.9888494399997</v>
       </c>
       <c r="Q54">
-        <v>1768.10404096</v>
+        <v>1765.08884944</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1295202497779748</v>
+        <v>0.1309483912511429</v>
       </c>
       <c r="T54">
-        <v>1.09115551012274</v>
+        <v>1.109768981078869</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.402157422235906</v>
+        <v>6.281361999174851</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08026004388803716</v>
+        <v>0.07998916788264643</v>
       </c>
       <c r="C55">
-        <v>6457.031571943414</v>
+        <v>6455.326429810778</v>
       </c>
       <c r="D55">
-        <v>10562.70757194341</v>
+        <v>10646.39442981078</v>
       </c>
       <c r="E55">
-        <v>1653.076000000001</v>
+        <v>1738.468000000001</v>
       </c>
       <c r="F55">
-        <v>4525.776000000001</v>
+        <v>4611.168000000001</v>
       </c>
       <c r="G55">
         <v>420.1</v>
@@ -5803,28 +5803,28 @@
         <v>1520.9</v>
       </c>
       <c r="M55">
-        <v>242.129016</v>
+        <v>246.697488</v>
       </c>
       <c r="N55">
-        <v>1278.770984</v>
+        <v>1274.202512</v>
       </c>
       <c r="O55">
-        <v>434.7821345599999</v>
+        <v>433.2288540799999</v>
       </c>
       <c r="P55">
-        <v>843.9888494399997</v>
+        <v>840.9736579199997</v>
       </c>
       <c r="Q55">
-        <v>1765.08884944</v>
+        <v>1762.07365792</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1309483912511429</v>
+        <v>0.1324386258318401</v>
       </c>
       <c r="T55">
-        <v>1.109768981078869</v>
+        <v>1.129191733380917</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.281361999174851</v>
+        <v>6.165040480671613</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07998916788264643</v>
+        <v>0.07971829187725568</v>
       </c>
       <c r="C56">
-        <v>6455.326429810778</v>
+        <v>6454.957956508338</v>
       </c>
       <c r="D56">
-        <v>10646.39442981078</v>
+        <v>10731.41795650834</v>
       </c>
       <c r="E56">
-        <v>1738.468000000001</v>
+        <v>1823.860000000001</v>
       </c>
       <c r="F56">
-        <v>4611.168000000001</v>
+        <v>4696.56</v>
       </c>
       <c r="G56">
         <v>420.1</v>
@@ -5885,28 +5885,28 @@
         <v>1520.9</v>
       </c>
       <c r="M56">
-        <v>246.697488</v>
+        <v>251.26596</v>
       </c>
       <c r="N56">
-        <v>1274.202512</v>
+        <v>1269.63404</v>
       </c>
       <c r="O56">
-        <v>433.2288540799999</v>
+        <v>431.6755736</v>
       </c>
       <c r="P56">
-        <v>840.9736579199997</v>
+        <v>837.9584663999997</v>
       </c>
       <c r="Q56">
-        <v>1762.07365792</v>
+        <v>1759.0584664</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1324386258318401</v>
+        <v>0.1339950930605682</v>
       </c>
       <c r="T56">
-        <v>1.129191733380917</v>
+        <v>1.149477719118611</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.165040480671613</v>
+        <v>6.052948835568493</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07971829187725568</v>
+        <v>0.07944741587186495</v>
       </c>
       <c r="C57">
-        <v>6454.957956508338</v>
+        <v>6455.958434293474</v>
       </c>
       <c r="D57">
-        <v>10731.41795650834</v>
+        <v>10817.81043429347</v>
       </c>
       <c r="E57">
-        <v>1823.860000000001</v>
+        <v>1909.252000000001</v>
       </c>
       <c r="F57">
-        <v>4696.56</v>
+        <v>4781.952000000001</v>
       </c>
       <c r="G57">
         <v>420.1</v>
@@ -5967,28 +5967,28 @@
         <v>1520.9</v>
       </c>
       <c r="M57">
-        <v>251.26596</v>
+        <v>255.834432</v>
       </c>
       <c r="N57">
-        <v>1269.63404</v>
+        <v>1265.065568</v>
       </c>
       <c r="O57">
-        <v>431.6755736</v>
+        <v>430.1222931199999</v>
       </c>
       <c r="P57">
-        <v>837.9584663999997</v>
+        <v>834.9432748799996</v>
       </c>
       <c r="Q57">
-        <v>1759.0584664</v>
+        <v>1756.043274879999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1339950930605682</v>
+        <v>0.1356223087996931</v>
       </c>
       <c r="T57">
-        <v>1.149477719118611</v>
+        <v>1.170685795117109</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.052948835568493</v>
+        <v>5.944860463504769</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07944741587186495</v>
+        <v>0.07917653986647422</v>
       </c>
       <c r="C58">
-        <v>6455.958434293474</v>
+        <v>6458.361193403869</v>
       </c>
       <c r="D58">
-        <v>10817.81043429347</v>
+        <v>10905.60519340387</v>
       </c>
       <c r="E58">
-        <v>1909.252000000001</v>
+        <v>1994.644000000001</v>
       </c>
       <c r="F58">
-        <v>4781.952000000001</v>
+        <v>4867.344000000001</v>
       </c>
       <c r="G58">
         <v>420.1</v>
@@ -6049,28 +6049,28 @@
         <v>1520.9</v>
       </c>
       <c r="M58">
-        <v>255.834432</v>
+        <v>260.402904</v>
       </c>
       <c r="N58">
-        <v>1265.065568</v>
+        <v>1260.497096</v>
       </c>
       <c r="O58">
-        <v>430.1222931199999</v>
+        <v>428.5690126399999</v>
       </c>
       <c r="P58">
-        <v>834.9432748799996</v>
+        <v>831.9280833599997</v>
       </c>
       <c r="Q58">
-        <v>1756.043274879999</v>
+        <v>1753.02808336</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1356223087996931</v>
+        <v>0.1373252089918005</v>
       </c>
       <c r="T58">
-        <v>1.170685795117109</v>
+        <v>1.192880293255073</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.944860463504769</v>
+        <v>5.840564665899422</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07917653986647422</v>
+        <v>0.07890566386108347</v>
       </c>
       <c r="C59">
-        <v>6458.361193403869</v>
+        <v>6462.200654931225</v>
       </c>
       <c r="D59">
-        <v>10905.60519340387</v>
+        <v>10994.83665493122</v>
       </c>
       <c r="E59">
-        <v>1994.644000000001</v>
+        <v>2080.036000000001</v>
       </c>
       <c r="F59">
-        <v>4867.344000000001</v>
+        <v>4952.736000000001</v>
       </c>
       <c r="G59">
         <v>420.1</v>
@@ -6131,28 +6131,28 @@
         <v>1520.9</v>
       </c>
       <c r="M59">
-        <v>260.402904</v>
+        <v>264.971376</v>
       </c>
       <c r="N59">
-        <v>1260.497096</v>
+        <v>1255.928624</v>
       </c>
       <c r="O59">
-        <v>428.5690126399999</v>
+        <v>427.0157321599999</v>
       </c>
       <c r="P59">
-        <v>831.9280833599997</v>
+        <v>828.9128918399997</v>
       </c>
       <c r="Q59">
-        <v>1753.02808336</v>
+        <v>1750.01289184</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1373252089918005</v>
+        <v>0.1391091996692464</v>
       </c>
       <c r="T59">
-        <v>1.192880293255073</v>
+        <v>1.216131672256749</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.840564665899422</v>
+        <v>5.739865275108054</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07890566386108348</v>
+        <v>0.07863478785569274</v>
       </c>
       <c r="C60">
-        <v>6462.20065493122</v>
+        <v>6467.51237581715</v>
       </c>
       <c r="D60">
-        <v>10994.83665493122</v>
+        <v>11085.54037581715</v>
       </c>
       <c r="E60">
-        <v>2080.036</v>
+        <v>2165.428000000001</v>
       </c>
       <c r="F60">
-        <v>4952.736</v>
+        <v>5038.128000000001</v>
       </c>
       <c r="G60">
         <v>420.1</v>
@@ -6213,28 +6213,28 @@
         <v>1520.9</v>
       </c>
       <c r="M60">
-        <v>264.971376</v>
+        <v>269.539848</v>
       </c>
       <c r="N60">
-        <v>1255.928624</v>
+        <v>1251.360152</v>
       </c>
       <c r="O60">
-        <v>427.0157321599999</v>
+        <v>425.46245168</v>
       </c>
       <c r="P60">
-        <v>828.9128918399997</v>
+        <v>825.8977003199998</v>
       </c>
       <c r="Q60">
-        <v>1750.01289184</v>
+        <v>1746.99770032</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1391091996692464</v>
+        <v>0.1409802142821774</v>
       </c>
       <c r="T60">
-        <v>1.216131672256748</v>
+        <v>1.240517264868262</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.739865275108055</v>
+        <v>5.642579422987579</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07863478785569274</v>
+        <v>0.078680711850302</v>
       </c>
       <c r="C61">
-        <v>6467.51237581715</v>
+        <v>6366.637368673708</v>
       </c>
       <c r="D61">
-        <v>11085.54037581715</v>
+        <v>11070.05736867371</v>
       </c>
       <c r="E61">
-        <v>2165.428000000001</v>
+        <v>2250.820000000001</v>
       </c>
       <c r="F61">
-        <v>5038.128000000001</v>
+        <v>5123.52</v>
       </c>
       <c r="G61">
         <v>420.1</v>
@@ -6295,45 +6295,45 @@
         <v>1520.9</v>
       </c>
       <c r="M61">
-        <v>269.539848</v>
+        <v>278.207136</v>
       </c>
       <c r="N61">
-        <v>1251.360152</v>
+        <v>1242.692864</v>
       </c>
       <c r="O61">
-        <v>425.46245168</v>
+        <v>422.5155737599999</v>
       </c>
       <c r="P61">
-        <v>825.8977003199998</v>
+        <v>820.1772902399998</v>
       </c>
       <c r="Q61">
-        <v>1746.99770032</v>
+        <v>1741.27729024</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1409802142821774</v>
+        <v>0.142944779625755</v>
       </c>
       <c r="T61">
-        <v>1.240517264868262</v>
+        <v>1.266122137110352</v>
       </c>
       <c r="U61">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V61">
         <v>0.34</v>
       </c>
       <c r="W61">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y61">
-        <v>5.642579422987579</v>
+        <v>5.466790039490574</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.078680711850302</v>
+        <v>0.07841511584491127</v>
       </c>
       <c r="C62">
-        <v>6366.637368673708</v>
+        <v>6371.392619124899</v>
       </c>
       <c r="D62">
-        <v>11070.05736867371</v>
+        <v>11160.2046191249</v>
       </c>
       <c r="E62">
-        <v>2250.820000000001</v>
+        <v>2336.212</v>
       </c>
       <c r="F62">
-        <v>5123.52</v>
+        <v>5208.912</v>
       </c>
       <c r="G62">
         <v>420.1</v>
@@ -6377,28 +6377,28 @@
         <v>1520.9</v>
       </c>
       <c r="M62">
-        <v>278.207136</v>
+        <v>282.8439216</v>
       </c>
       <c r="N62">
-        <v>1242.692864</v>
+        <v>1238.056078399999</v>
       </c>
       <c r="O62">
-        <v>422.5155737599999</v>
+        <v>420.9390666559999</v>
       </c>
       <c r="P62">
-        <v>820.1772902399998</v>
+        <v>817.1170117439997</v>
       </c>
       <c r="Q62">
-        <v>1741.27729024</v>
+        <v>1738.217011744</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.142944779625755</v>
+        <v>0.1450100919100289</v>
       </c>
       <c r="T62">
-        <v>1.266122137110352</v>
+        <v>1.29304007972383</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.466790039490574</v>
+        <v>5.377170530646466</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07841511584491127</v>
+        <v>0.07814951983952054</v>
       </c>
       <c r="C63">
-        <v>6371.392619124899</v>
+        <v>6377.628123362587</v>
       </c>
       <c r="D63">
-        <v>11160.2046191249</v>
+        <v>11251.83212336259</v>
       </c>
       <c r="E63">
-        <v>2336.212</v>
+        <v>2421.604</v>
       </c>
       <c r="F63">
-        <v>5208.912</v>
+        <v>5294.304</v>
       </c>
       <c r="G63">
         <v>420.1</v>
@@ -6459,28 +6459,28 @@
         <v>1520.9</v>
       </c>
       <c r="M63">
-        <v>282.8439216</v>
+        <v>287.4807072</v>
       </c>
       <c r="N63">
-        <v>1238.056078399999</v>
+        <v>1233.4192928</v>
       </c>
       <c r="O63">
-        <v>420.9390666559999</v>
+        <v>419.3625595519999</v>
       </c>
       <c r="P63">
-        <v>817.1170117439997</v>
+        <v>814.0567332479998</v>
       </c>
       <c r="Q63">
-        <v>1738.217011744</v>
+        <v>1735.156733248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1450100919100289</v>
+        <v>0.1471841048408435</v>
       </c>
       <c r="T63">
-        <v>1.29304007972383</v>
+        <v>1.321374756159071</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.377170530646466</v>
+        <v>5.290441973700557</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07814951983952054</v>
+        <v>0.07788392383412979</v>
       </c>
       <c r="C64">
-        <v>6377.628123362587</v>
+        <v>6385.380642740652</v>
       </c>
       <c r="D64">
-        <v>11251.83212336259</v>
+        <v>11344.97664274065</v>
       </c>
       <c r="E64">
-        <v>2421.604</v>
+        <v>2506.996000000001</v>
       </c>
       <c r="F64">
-        <v>5294.304</v>
+        <v>5379.696000000001</v>
       </c>
       <c r="G64">
         <v>420.1</v>
@@ -6541,28 +6541,28 @@
         <v>1520.9</v>
       </c>
       <c r="M64">
-        <v>287.4807072</v>
+        <v>292.1174928</v>
       </c>
       <c r="N64">
-        <v>1233.4192928</v>
+        <v>1228.7825072</v>
       </c>
       <c r="O64">
-        <v>419.3625595519999</v>
+        <v>417.7860524479999</v>
       </c>
       <c r="P64">
-        <v>814.0567332479998</v>
+        <v>810.9964547519996</v>
       </c>
       <c r="Q64">
-        <v>1735.156733248</v>
+        <v>1732.096454752</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1471841048408435</v>
+        <v>0.1494756319841346</v>
       </c>
       <c r="T64">
-        <v>1.321374756159071</v>
+        <v>1.351241036725946</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.290441973700557</v>
+        <v>5.206466704276737</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07788392383412979</v>
+        <v>0.07761832782873905</v>
       </c>
       <c r="C65">
-        <v>6385.380642740652</v>
+        <v>6394.688166039971</v>
       </c>
       <c r="D65">
-        <v>11344.97664274065</v>
+        <v>11439.67616603997</v>
       </c>
       <c r="E65">
-        <v>2506.996000000001</v>
+        <v>2592.388000000001</v>
       </c>
       <c r="F65">
-        <v>5379.696000000001</v>
+        <v>5465.088000000001</v>
       </c>
       <c r="G65">
         <v>420.1</v>
@@ -6623,28 +6623,28 @@
         <v>1520.9</v>
       </c>
       <c r="M65">
-        <v>292.1174928</v>
+        <v>296.7542784</v>
       </c>
       <c r="N65">
-        <v>1228.7825072</v>
+        <v>1224.1457216</v>
       </c>
       <c r="O65">
-        <v>417.7860524479999</v>
+        <v>416.2095453439999</v>
       </c>
       <c r="P65">
-        <v>810.9964547519996</v>
+        <v>807.9361762559997</v>
       </c>
       <c r="Q65">
-        <v>1732.096454752</v>
+        <v>1729.036176256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1494756319841346</v>
+        <v>0.1518944661909418</v>
       </c>
       <c r="T65">
-        <v>1.351241036725946</v>
+        <v>1.382766555102093</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.206466704276737</v>
+        <v>5.125115662022413</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07761832782873905</v>
+        <v>0.07735273182334833</v>
       </c>
       <c r="C66">
-        <v>6394.688166039971</v>
+        <v>6405.589961127957</v>
       </c>
       <c r="D66">
-        <v>11439.67616603997</v>
+        <v>11535.96996112796</v>
       </c>
       <c r="E66">
-        <v>2592.388000000001</v>
+        <v>2677.780000000001</v>
       </c>
       <c r="F66">
-        <v>5465.088000000001</v>
+        <v>5550.48</v>
       </c>
       <c r="G66">
         <v>420.1</v>
@@ -6705,28 +6705,28 @@
         <v>1520.9</v>
       </c>
       <c r="M66">
-        <v>296.7542784</v>
+        <v>301.391064</v>
       </c>
       <c r="N66">
-        <v>1224.1457216</v>
+        <v>1219.508936</v>
       </c>
       <c r="O66">
-        <v>416.2095453439999</v>
+        <v>414.63303824</v>
       </c>
       <c r="P66">
-        <v>807.9361762559997</v>
+        <v>804.8758977599998</v>
       </c>
       <c r="Q66">
-        <v>1729.036176256</v>
+        <v>1725.97589776</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1518944661909418</v>
+        <v>0.1544515194952809</v>
       </c>
       <c r="T66">
-        <v>1.382766555102093</v>
+        <v>1.416093531671162</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.125115662022413</v>
+        <v>5.04626772876053</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07735273182334833</v>
+        <v>0.07708713581795758</v>
       </c>
       <c r="C67">
-        <v>6405.589961127957</v>
+        <v>6418.126629249272</v>
       </c>
       <c r="D67">
-        <v>11535.96996112796</v>
+        <v>11633.89862924927</v>
       </c>
       <c r="E67">
-        <v>2677.780000000001</v>
+        <v>2763.172</v>
       </c>
       <c r="F67">
-        <v>5550.48</v>
+        <v>5635.872</v>
       </c>
       <c r="G67">
         <v>420.1</v>
@@ -6787,28 +6787,28 @@
         <v>1520.9</v>
       </c>
       <c r="M67">
-        <v>301.391064</v>
+        <v>306.0278496</v>
       </c>
       <c r="N67">
-        <v>1219.508936</v>
+        <v>1214.8721504</v>
       </c>
       <c r="O67">
-        <v>414.63303824</v>
+        <v>413.0565311359999</v>
       </c>
       <c r="P67">
-        <v>804.8758977599998</v>
+        <v>801.8156192639997</v>
       </c>
       <c r="Q67">
-        <v>1725.97589776</v>
+        <v>1722.915619264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1544515194952809</v>
+        <v>0.1571589876998752</v>
       </c>
       <c r="T67">
-        <v>1.416093531671162</v>
+        <v>1.451380918626646</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.04626772876053</v>
+        <v>4.969809126809613</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07708713581795758</v>
+        <v>0.07682153981256684</v>
       </c>
       <c r="C68">
-        <v>6418.126629249272</v>
+        <v>6432.340162105435</v>
       </c>
       <c r="D68">
-        <v>11633.89862924927</v>
+        <v>11733.50416210544</v>
       </c>
       <c r="E68">
-        <v>2763.172</v>
+        <v>2848.564000000001</v>
       </c>
       <c r="F68">
-        <v>5635.872</v>
+        <v>5721.264000000001</v>
       </c>
       <c r="G68">
         <v>420.1</v>
@@ -6869,28 +6869,28 @@
         <v>1520.9</v>
       </c>
       <c r="M68">
-        <v>306.0278496</v>
+        <v>310.6646352000001</v>
       </c>
       <c r="N68">
-        <v>1214.8721504</v>
+        <v>1210.2353648</v>
       </c>
       <c r="O68">
-        <v>413.0565311359999</v>
+        <v>411.4800240319999</v>
       </c>
       <c r="P68">
-        <v>801.8156192639997</v>
+        <v>798.7553407679998</v>
       </c>
       <c r="Q68">
-        <v>1722.915619264</v>
+        <v>1719.855340768</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1571589876998752</v>
+        <v>0.1600305448865662</v>
       </c>
       <c r="T68">
-        <v>1.451380918626646</v>
+        <v>1.488806935094585</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.969809126809613</v>
+        <v>4.895632871185589</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07682153981256684</v>
+        <v>0.07655594380717609</v>
       </c>
       <c r="C69">
-        <v>6432.340162105435</v>
+        <v>6448.274001892014</v>
       </c>
       <c r="D69">
-        <v>11733.50416210544</v>
+        <v>11834.83000189201</v>
       </c>
       <c r="E69">
-        <v>2848.564000000001</v>
+        <v>2933.956000000001</v>
       </c>
       <c r="F69">
-        <v>5721.264000000001</v>
+        <v>5806.656000000001</v>
       </c>
       <c r="G69">
         <v>420.1</v>
@@ -6951,28 +6951,28 @@
         <v>1520.9</v>
       </c>
       <c r="M69">
-        <v>310.6646352000001</v>
+        <v>315.3014208000001</v>
       </c>
       <c r="N69">
-        <v>1210.2353648</v>
+        <v>1205.5985792</v>
       </c>
       <c r="O69">
-        <v>411.4800240319999</v>
+        <v>409.9035169279999</v>
       </c>
       <c r="P69">
-        <v>798.7553407679998</v>
+        <v>795.6950622719997</v>
       </c>
       <c r="Q69">
-        <v>1719.855340768</v>
+        <v>1716.795062272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1600305448865662</v>
+        <v>0.1630815743974253</v>
       </c>
       <c r="T69">
-        <v>1.488806935094585</v>
+        <v>1.528572077591769</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.895632871185589</v>
+        <v>4.823638270138741</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07655594380717609</v>
+        <v>0.07629034780178537</v>
       </c>
       <c r="C70">
-        <v>6448.274001892014</v>
+        <v>6465.973104473556</v>
       </c>
       <c r="D70">
-        <v>11834.83000189201</v>
+        <v>11937.92110447356</v>
       </c>
       <c r="E70">
-        <v>2933.956000000001</v>
+        <v>3019.348000000001</v>
       </c>
       <c r="F70">
-        <v>5806.656000000001</v>
+        <v>5892.048000000001</v>
       </c>
       <c r="G70">
         <v>420.1</v>
@@ -7033,28 +7033,28 @@
         <v>1520.9</v>
       </c>
       <c r="M70">
-        <v>315.3014208000001</v>
+        <v>319.9382064000001</v>
       </c>
       <c r="N70">
-        <v>1205.5985792</v>
+        <v>1200.9617936</v>
       </c>
       <c r="O70">
-        <v>409.9035169279999</v>
+        <v>408.3270098239998</v>
       </c>
       <c r="P70">
-        <v>795.6950622719997</v>
+        <v>792.6347837759997</v>
       </c>
       <c r="Q70">
-        <v>1716.795062272</v>
+        <v>1713.734783776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1630815743974253</v>
+        <v>0.1663294445218883</v>
       </c>
       <c r="T70">
-        <v>1.528572077591769</v>
+        <v>1.570902713153288</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.823638270138741</v>
+        <v>4.753730469122237</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07629034780178537</v>
+        <v>0.07602475179639462</v>
       </c>
       <c r="C71">
-        <v>6465.973104473556</v>
+        <v>6485.484005889487</v>
       </c>
       <c r="D71">
-        <v>11937.92110447356</v>
+        <v>12042.82400588949</v>
       </c>
       <c r="E71">
-        <v>3019.348000000001</v>
+        <v>3104.740000000002</v>
       </c>
       <c r="F71">
-        <v>5892.048000000001</v>
+        <v>5977.440000000001</v>
       </c>
       <c r="G71">
         <v>420.1</v>
@@ -7115,28 +7115,28 @@
         <v>1520.9</v>
       </c>
       <c r="M71">
-        <v>319.9382064000001</v>
+        <v>324.5749920000001</v>
       </c>
       <c r="N71">
-        <v>1200.9617936</v>
+        <v>1196.325008</v>
       </c>
       <c r="O71">
-        <v>408.3270098239998</v>
+        <v>406.7505027199999</v>
       </c>
       <c r="P71">
-        <v>792.6347837759997</v>
+        <v>789.5745052799997</v>
       </c>
       <c r="Q71">
-        <v>1713.734783776</v>
+        <v>1710.67450528</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1663294445218883</v>
+        <v>0.1697938393213154</v>
       </c>
       <c r="T71">
-        <v>1.570902713153288</v>
+        <v>1.616055391085575</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.753730469122237</v>
+        <v>4.685820033849063</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07602475179639462</v>
+        <v>0.0757591557910039</v>
       </c>
       <c r="C72">
-        <v>6485.484005889487</v>
+        <v>6506.854892397397</v>
       </c>
       <c r="D72">
-        <v>12042.82400588949</v>
+        <v>12149.5868923974</v>
       </c>
       <c r="E72">
-        <v>3104.740000000002</v>
+        <v>3190.132000000001</v>
       </c>
       <c r="F72">
-        <v>5977.440000000001</v>
+        <v>6062.832000000001</v>
       </c>
       <c r="G72">
         <v>420.1</v>
@@ -7197,28 +7197,28 @@
         <v>1520.9</v>
       </c>
       <c r="M72">
-        <v>324.5749920000001</v>
+        <v>329.2117776000001</v>
       </c>
       <c r="N72">
-        <v>1196.325008</v>
+        <v>1191.6882224</v>
       </c>
       <c r="O72">
-        <v>406.7505027199999</v>
+        <v>405.1739956159999</v>
       </c>
       <c r="P72">
-        <v>789.5745052799997</v>
+        <v>786.5142267839997</v>
       </c>
       <c r="Q72">
-        <v>1710.67450528</v>
+        <v>1707.614226784</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1697938393213154</v>
+        <v>0.1734971579000135</v>
       </c>
       <c r="T72">
-        <v>1.616055391085575</v>
+        <v>1.664322046806295</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.685820033849063</v>
+        <v>4.619822568583583</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0757591557910039</v>
+        <v>0.07549355978561316</v>
       </c>
       <c r="C73">
-        <v>6506.854892397398</v>
+        <v>6530.135674275569</v>
       </c>
       <c r="D73">
-        <v>12149.5868923974</v>
+        <v>12258.25967427557</v>
       </c>
       <c r="E73">
-        <v>3190.132000000001</v>
+        <v>3275.524</v>
       </c>
       <c r="F73">
-        <v>6062.832</v>
+        <v>6148.224</v>
       </c>
       <c r="G73">
         <v>420.1</v>
@@ -7279,28 +7279,28 @@
         <v>1520.9</v>
       </c>
       <c r="M73">
-        <v>329.2117776</v>
+        <v>333.8485632</v>
       </c>
       <c r="N73">
-        <v>1191.6882224</v>
+        <v>1187.0514368</v>
       </c>
       <c r="O73">
-        <v>405.1739956159999</v>
+        <v>403.5974885119999</v>
       </c>
       <c r="P73">
-        <v>786.5142267839997</v>
+        <v>783.4539482879998</v>
       </c>
       <c r="Q73">
-        <v>1707.614226784</v>
+        <v>1704.553948288</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1734971579000134</v>
+        <v>0.1774649992343327</v>
       </c>
       <c r="T73">
-        <v>1.664322046806295</v>
+        <v>1.716036320792781</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.619822568583584</v>
+        <v>4.555658366242145</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07549355978561316</v>
+        <v>0.07522796378022242</v>
       </c>
       <c r="C74">
-        <v>6530.135674275569</v>
+        <v>6555.378063621871</v>
       </c>
       <c r="D74">
-        <v>12258.25967427557</v>
+        <v>12368.89406362187</v>
       </c>
       <c r="E74">
-        <v>3275.524</v>
+        <v>3360.916</v>
       </c>
       <c r="F74">
-        <v>6148.224</v>
+        <v>6233.616</v>
       </c>
       <c r="G74">
         <v>420.1</v>
@@ -7361,28 +7361,28 @@
         <v>1520.9</v>
       </c>
       <c r="M74">
-        <v>333.8485632</v>
+        <v>338.4853488</v>
       </c>
       <c r="N74">
-        <v>1187.0514368</v>
+        <v>1182.4146512</v>
       </c>
       <c r="O74">
-        <v>403.5974885119999</v>
+        <v>402.020981408</v>
       </c>
       <c r="P74">
-        <v>783.4539482879998</v>
+        <v>780.3936697919999</v>
       </c>
       <c r="Q74">
-        <v>1704.553948288</v>
+        <v>1701.493669792</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1774649992343327</v>
+        <v>0.1817267547415645</v>
       </c>
       <c r="T74">
-        <v>1.716036320792781</v>
+        <v>1.771581281741229</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.555658366242145</v>
+        <v>4.493252087252527</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07522796378022242</v>
+        <v>0.07496236777483167</v>
       </c>
       <c r="C75">
-        <v>6555.378063621871</v>
+        <v>6582.635656404063</v>
       </c>
       <c r="D75">
-        <v>12368.89406362187</v>
+        <v>12481.54365640406</v>
       </c>
       <c r="E75">
-        <v>3360.916</v>
+        <v>3446.308000000001</v>
       </c>
       <c r="F75">
-        <v>6233.616</v>
+        <v>6319.008000000001</v>
       </c>
       <c r="G75">
         <v>420.1</v>
@@ -7443,28 +7443,28 @@
         <v>1520.9</v>
       </c>
       <c r="M75">
-        <v>338.4853488</v>
+        <v>343.1221344</v>
       </c>
       <c r="N75">
-        <v>1182.4146512</v>
+        <v>1177.7778656</v>
       </c>
       <c r="O75">
-        <v>402.020981408</v>
+        <v>400.4444743039999</v>
       </c>
       <c r="P75">
-        <v>780.3936697919999</v>
+        <v>777.3333912959997</v>
       </c>
       <c r="Q75">
-        <v>1701.493669792</v>
+        <v>1698.433391296</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1817267547415645</v>
+        <v>0.1863163375955065</v>
       </c>
       <c r="T75">
-        <v>1.771581281741229</v>
+        <v>1.831398931993404</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.493252087252527</v>
+        <v>4.432532464451817</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07496236777483167</v>
+        <v>0.07469677176944094</v>
       </c>
       <c r="C76">
-        <v>6582.635656404063</v>
+        <v>6611.964019034906</v>
       </c>
       <c r="D76">
-        <v>12481.54365640406</v>
+        <v>12596.26401903491</v>
       </c>
       <c r="E76">
-        <v>3446.308000000001</v>
+        <v>3531.700000000001</v>
       </c>
       <c r="F76">
-        <v>6319.008000000001</v>
+        <v>6404.400000000001</v>
       </c>
       <c r="G76">
         <v>420.1</v>
@@ -7525,28 +7525,28 @@
         <v>1520.9</v>
       </c>
       <c r="M76">
-        <v>343.1221344</v>
+        <v>347.75892</v>
       </c>
       <c r="N76">
-        <v>1177.7778656</v>
+        <v>1173.14108</v>
       </c>
       <c r="O76">
-        <v>400.4444743039999</v>
+        <v>398.8679671999999</v>
       </c>
       <c r="P76">
-        <v>777.3333912959997</v>
+        <v>774.2731127999998</v>
       </c>
       <c r="Q76">
-        <v>1698.433391296</v>
+        <v>1695.3731128</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1863163375955065</v>
+        <v>0.1912730870777638</v>
       </c>
       <c r="T76">
-        <v>1.831398931993404</v>
+        <v>1.896001994265753</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.432532464451817</v>
+        <v>4.37343203159246</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07469677176944094</v>
+        <v>0.0744311757640502</v>
       </c>
       <c r="C77">
-        <v>6611.964019034906</v>
+        <v>6643.420779765977</v>
       </c>
       <c r="D77">
-        <v>12596.26401903491</v>
+        <v>12713.11277976598</v>
       </c>
       <c r="E77">
-        <v>3531.700000000001</v>
+        <v>3617.092000000001</v>
       </c>
       <c r="F77">
-        <v>6404.400000000001</v>
+        <v>6489.792</v>
       </c>
       <c r="G77">
         <v>420.1</v>
@@ -7607,28 +7607,28 @@
         <v>1520.9</v>
       </c>
       <c r="M77">
-        <v>347.75892</v>
+        <v>352.3957056</v>
       </c>
       <c r="N77">
-        <v>1173.14108</v>
+        <v>1168.5042944</v>
       </c>
       <c r="O77">
-        <v>398.8679671999999</v>
+        <v>397.2914600959999</v>
       </c>
       <c r="P77">
-        <v>774.2731127999998</v>
+        <v>771.2128343039998</v>
       </c>
       <c r="Q77">
-        <v>1695.3731128</v>
+        <v>1692.312834304</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1912730870777638</v>
+        <v>0.1966428990168759</v>
       </c>
       <c r="T77">
-        <v>1.896001994265753</v>
+        <v>1.965988645060797</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.37343203159246</v>
+        <v>4.315886873282032</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0744311757640502</v>
+        <v>0.07416557975865946</v>
       </c>
       <c r="C78">
-        <v>6643.420779765977</v>
+        <v>6677.065725215927</v>
       </c>
       <c r="D78">
-        <v>12713.11277976598</v>
+        <v>12832.14972521593</v>
       </c>
       <c r="E78">
-        <v>3617.092000000001</v>
+        <v>3702.484000000001</v>
       </c>
       <c r="F78">
-        <v>6489.792</v>
+        <v>6575.184000000001</v>
       </c>
       <c r="G78">
         <v>420.1</v>
@@ -7689,28 +7689,28 @@
         <v>1520.9</v>
       </c>
       <c r="M78">
-        <v>352.3957056</v>
+        <v>357.0324912000001</v>
       </c>
       <c r="N78">
-        <v>1168.5042944</v>
+        <v>1163.8675088</v>
       </c>
       <c r="O78">
-        <v>397.2914600959999</v>
+        <v>395.7149529919999</v>
       </c>
       <c r="P78">
-        <v>771.2128343039998</v>
+        <v>768.1525558079996</v>
       </c>
       <c r="Q78">
-        <v>1692.312834304</v>
+        <v>1689.252555808</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1966428990168759</v>
+        <v>0.2024796511246064</v>
       </c>
       <c r="T78">
-        <v>1.965988645060797</v>
+        <v>2.04206109157715</v>
       </c>
       <c r="U78">
         <v>0.0543</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.315886873282032</v>
+        <v>4.259836394408239</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07416557975865946</v>
+        <v>0.07441478375326874</v>
       </c>
       <c r="C79">
-        <v>6677.065725215927</v>
+        <v>6479.919500598284</v>
       </c>
       <c r="D79">
-        <v>12832.14972521593</v>
+        <v>12720.39550059828</v>
       </c>
       <c r="E79">
-        <v>3702.484000000001</v>
+        <v>3787.876000000001</v>
       </c>
       <c r="F79">
-        <v>6575.184000000001</v>
+        <v>6660.576000000001</v>
       </c>
       <c r="G79">
         <v>420.1</v>
@@ -7771,45 +7771,45 @@
         <v>1520.9</v>
       </c>
       <c r="M79">
-        <v>357.0324912000001</v>
+        <v>368.3298528000001</v>
       </c>
       <c r="N79">
-        <v>1163.8675088</v>
+        <v>1152.5701472</v>
       </c>
       <c r="O79">
-        <v>395.7149529919999</v>
+        <v>391.8738500479999</v>
       </c>
       <c r="P79">
-        <v>768.1525558079996</v>
+        <v>760.6962971519997</v>
       </c>
       <c r="Q79">
-        <v>1689.252555808</v>
+        <v>1681.796297152</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2024796511246064</v>
+        <v>0.2088470170603124</v>
       </c>
       <c r="T79">
-        <v>2.04206109157715</v>
+        <v>2.125049215049535</v>
       </c>
       <c r="U79">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V79">
         <v>0.34</v>
       </c>
       <c r="W79">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.259836394408239</v>
+        <v>4.129179289808571</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07441478375326874</v>
+        <v>0.074155787747878</v>
       </c>
       <c r="C80">
-        <v>6479.919500598284</v>
+        <v>6510.713009212546</v>
       </c>
       <c r="D80">
-        <v>12720.39550059828</v>
+        <v>12836.58100921255</v>
       </c>
       <c r="E80">
-        <v>3787.876000000001</v>
+        <v>3873.268000000001</v>
       </c>
       <c r="F80">
-        <v>6660.576000000001</v>
+        <v>6745.968000000001</v>
       </c>
       <c r="G80">
         <v>420.1</v>
@@ -7853,28 +7853,28 @@
         <v>1520.9</v>
       </c>
       <c r="M80">
-        <v>368.3298528000001</v>
+        <v>373.0520304</v>
       </c>
       <c r="N80">
-        <v>1152.5701472</v>
+        <v>1147.847969599999</v>
       </c>
       <c r="O80">
-        <v>391.8738500479999</v>
+        <v>390.2683096639998</v>
       </c>
       <c r="P80">
-        <v>760.6962971519997</v>
+        <v>757.5796599359996</v>
       </c>
       <c r="Q80">
-        <v>1681.796297152</v>
+        <v>1678.679659936</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2088470170603124</v>
+        <v>0.2158207987994191</v>
       </c>
       <c r="T80">
-        <v>2.125049215049535</v>
+        <v>2.215940969328814</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.129179289808571</v>
+        <v>4.076911197532513</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.074155787747878</v>
+        <v>0.07389679174248726</v>
       </c>
       <c r="C81">
-        <v>6510.713009212546</v>
+        <v>6543.648512036769</v>
       </c>
       <c r="D81">
-        <v>12836.58100921255</v>
+        <v>12954.90851203677</v>
       </c>
       <c r="E81">
-        <v>3873.268000000001</v>
+        <v>3958.660000000001</v>
       </c>
       <c r="F81">
-        <v>6745.968000000001</v>
+        <v>6831.360000000001</v>
       </c>
       <c r="G81">
         <v>420.1</v>
@@ -7935,28 +7935,28 @@
         <v>1520.9</v>
       </c>
       <c r="M81">
-        <v>373.0520304</v>
+        <v>377.774208</v>
       </c>
       <c r="N81">
-        <v>1147.847969599999</v>
+        <v>1143.125792</v>
       </c>
       <c r="O81">
-        <v>390.2683096639998</v>
+        <v>388.6627692799999</v>
       </c>
       <c r="P81">
-        <v>757.5796599359996</v>
+        <v>754.4630227199997</v>
       </c>
       <c r="Q81">
-        <v>1678.679659936</v>
+        <v>1675.563022719999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2158207987994191</v>
+        <v>0.2234919587124363</v>
       </c>
       <c r="T81">
-        <v>2.215940969328814</v>
+        <v>2.31592189903602</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.076911197532513</v>
+        <v>4.025949807563356</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07389679174248726</v>
+        <v>0.07363779573709653</v>
       </c>
       <c r="C82">
-        <v>6543.648512036769</v>
+        <v>6578.785794832985</v>
       </c>
       <c r="D82">
-        <v>12954.90851203677</v>
+        <v>13075.43779483299</v>
       </c>
       <c r="E82">
-        <v>3958.660000000001</v>
+        <v>4044.052000000001</v>
       </c>
       <c r="F82">
-        <v>6831.360000000001</v>
+        <v>6916.752000000001</v>
       </c>
       <c r="G82">
         <v>420.1</v>
@@ -8017,28 +8017,28 @@
         <v>1520.9</v>
       </c>
       <c r="M82">
-        <v>377.774208</v>
+        <v>382.4963856000001</v>
       </c>
       <c r="N82">
-        <v>1143.125792</v>
+        <v>1138.403614399999</v>
       </c>
       <c r="O82">
-        <v>388.6627692799999</v>
+        <v>387.0572288959999</v>
       </c>
       <c r="P82">
-        <v>754.4630227199997</v>
+        <v>751.3463855039996</v>
       </c>
       <c r="Q82">
-        <v>1675.563022719999</v>
+        <v>1672.446385503999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2234919587124363</v>
+        <v>0.2319706091426133</v>
       </c>
       <c r="T82">
-        <v>2.31592189903602</v>
+        <v>2.42642713713346</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.025949807563356</v>
+        <v>3.976246723519364</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07363779573709653</v>
+        <v>0.07337879973170579</v>
       </c>
       <c r="C83">
-        <v>6578.785794832985</v>
+        <v>6616.186889185949</v>
       </c>
       <c r="D83">
-        <v>13075.43779483299</v>
+        <v>13198.23088918595</v>
       </c>
       <c r="E83">
-        <v>4044.052000000001</v>
+        <v>4129.444000000001</v>
       </c>
       <c r="F83">
-        <v>6916.752000000001</v>
+        <v>7002.144000000001</v>
       </c>
       <c r="G83">
         <v>420.1</v>
@@ -8099,28 +8099,28 @@
         <v>1520.9</v>
       </c>
       <c r="M83">
-        <v>382.4963856000001</v>
+        <v>387.2185632000001</v>
       </c>
       <c r="N83">
-        <v>1138.403614399999</v>
+        <v>1133.6814368</v>
       </c>
       <c r="O83">
-        <v>387.0572288959999</v>
+        <v>385.4516885119999</v>
       </c>
       <c r="P83">
-        <v>751.3463855039996</v>
+        <v>748.2297482879997</v>
       </c>
       <c r="Q83">
-        <v>1672.446385503999</v>
+        <v>1669.329748288</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2319706091426133</v>
+        <v>0.24139133184281</v>
       </c>
       <c r="T83">
-        <v>2.42642713713346</v>
+        <v>2.549210735019503</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.976246723519364</v>
+        <v>3.927755909817909</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07337879973170579</v>
+        <v>0.07311980372631503</v>
       </c>
       <c r="C84">
-        <v>6616.186889185949</v>
+        <v>6655.916178956836</v>
       </c>
       <c r="D84">
-        <v>13198.23088918595</v>
+        <v>13323.35217895684</v>
       </c>
       <c r="E84">
-        <v>4129.444000000001</v>
+        <v>4214.836000000001</v>
       </c>
       <c r="F84">
-        <v>7002.144000000001</v>
+        <v>7087.536000000001</v>
       </c>
       <c r="G84">
         <v>420.1</v>
@@ -8181,28 +8181,28 @@
         <v>1520.9</v>
       </c>
       <c r="M84">
-        <v>387.2185632000001</v>
+        <v>391.9407408000001</v>
       </c>
       <c r="N84">
-        <v>1133.6814368</v>
+        <v>1128.959259199999</v>
       </c>
       <c r="O84">
-        <v>385.4516885119999</v>
+        <v>383.8461481279999</v>
       </c>
       <c r="P84">
-        <v>748.2297482879997</v>
+        <v>745.1131110719996</v>
       </c>
       <c r="Q84">
-        <v>1669.329748288</v>
+        <v>1666.213111071999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.24139133184281</v>
+        <v>0.2519203748606768</v>
       </c>
       <c r="T84">
-        <v>2.549210735019503</v>
+        <v>2.68643946206861</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.927755909817909</v>
+        <v>3.880433549458656</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07311980372631503</v>
+        <v>0.07286080772092431</v>
       </c>
       <c r="C85">
-        <v>6655.916178956836</v>
+        <v>6698.040512850132</v>
       </c>
       <c r="D85">
-        <v>13323.35217895684</v>
+        <v>13450.86851285013</v>
       </c>
       <c r="E85">
-        <v>4214.836000000001</v>
+        <v>4300.228000000002</v>
       </c>
       <c r="F85">
-        <v>7087.536000000001</v>
+        <v>7172.928000000002</v>
       </c>
       <c r="G85">
         <v>420.1</v>
@@ -8263,28 +8263,28 @@
         <v>1520.9</v>
       </c>
       <c r="M85">
-        <v>391.9407408000001</v>
+        <v>396.6629184000001</v>
       </c>
       <c r="N85">
-        <v>1128.959259199999</v>
+        <v>1124.2370816</v>
       </c>
       <c r="O85">
-        <v>383.8461481279999</v>
+        <v>382.2406077439999</v>
       </c>
       <c r="P85">
-        <v>745.1131110719996</v>
+        <v>741.9964738559997</v>
       </c>
       <c r="Q85">
-        <v>1666.213111071999</v>
+        <v>1663.096473856</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2519203748606768</v>
+        <v>0.263765548255777</v>
       </c>
       <c r="T85">
-        <v>2.68643946206861</v>
+        <v>2.840821779998856</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.880433549458656</v>
+        <v>3.834237911965101</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07286080772092432</v>
+        <v>0.07260181171553357</v>
       </c>
       <c r="C86">
-        <v>6698.040512850125</v>
+        <v>6742.629323507242</v>
       </c>
       <c r="D86">
-        <v>13450.86851285013</v>
+        <v>13580.84932350724</v>
       </c>
       <c r="E86">
-        <v>4300.228000000001</v>
+        <v>4385.620000000001</v>
       </c>
       <c r="F86">
-        <v>7172.928000000001</v>
+        <v>7258.320000000001</v>
       </c>
       <c r="G86">
         <v>420.1</v>
@@ -8345,28 +8345,28 @@
         <v>1520.9</v>
       </c>
       <c r="M86">
-        <v>396.6629184000001</v>
+        <v>401.385096</v>
       </c>
       <c r="N86">
-        <v>1124.2370816</v>
+        <v>1119.514904</v>
       </c>
       <c r="O86">
-        <v>382.2406077439999</v>
+        <v>380.6350673599999</v>
       </c>
       <c r="P86">
-        <v>741.9964738559997</v>
+        <v>738.8798366399997</v>
       </c>
       <c r="Q86">
-        <v>1663.096473856</v>
+        <v>1659.97983664</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2637655482557769</v>
+        <v>0.2771900781035571</v>
       </c>
       <c r="T86">
-        <v>2.840821779998854</v>
+        <v>3.015788406986466</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.834237911965101</v>
+        <v>3.789129230647865</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07260181171553357</v>
+        <v>0.07234281571014284</v>
       </c>
       <c r="C87">
-        <v>6742.629323507242</v>
+        <v>6789.75475357242</v>
       </c>
       <c r="D87">
-        <v>13580.84932350724</v>
+        <v>13713.36675357242</v>
       </c>
       <c r="E87">
-        <v>4385.620000000001</v>
+        <v>4471.012000000001</v>
       </c>
       <c r="F87">
-        <v>7258.320000000001</v>
+        <v>7343.712</v>
       </c>
       <c r="G87">
         <v>420.1</v>
@@ -8427,28 +8427,28 @@
         <v>1520.9</v>
       </c>
       <c r="M87">
-        <v>401.385096</v>
+        <v>406.1072736</v>
       </c>
       <c r="N87">
-        <v>1119.514904</v>
+        <v>1114.7927264</v>
       </c>
       <c r="O87">
-        <v>380.6350673599999</v>
+        <v>379.0295269759999</v>
       </c>
       <c r="P87">
-        <v>738.8798366399997</v>
+        <v>735.7631994239996</v>
       </c>
       <c r="Q87">
-        <v>1659.97983664</v>
+        <v>1656.863199424</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2771900781035571</v>
+        <v>0.2925323979295916</v>
       </c>
       <c r="T87">
-        <v>3.015788406986466</v>
+        <v>3.215750266400879</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.789129230647865</v>
+        <v>3.745069588431029</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07234281571014284</v>
+        <v>0.07208381970475208</v>
       </c>
       <c r="C88">
-        <v>6789.75475357242</v>
+        <v>6839.491789212222</v>
       </c>
       <c r="D88">
-        <v>13713.36675357242</v>
+        <v>13848.49578921222</v>
       </c>
       <c r="E88">
-        <v>4471.012000000001</v>
+        <v>4556.404</v>
       </c>
       <c r="F88">
-        <v>7343.712</v>
+        <v>7429.104</v>
       </c>
       <c r="G88">
         <v>420.1</v>
@@ -8509,28 +8509,28 @@
         <v>1520.9</v>
       </c>
       <c r="M88">
-        <v>406.1072736</v>
+        <v>410.8294512000001</v>
       </c>
       <c r="N88">
-        <v>1114.7927264</v>
+        <v>1110.0705488</v>
       </c>
       <c r="O88">
-        <v>379.0295269759999</v>
+        <v>377.4239865919999</v>
       </c>
       <c r="P88">
-        <v>735.7631994239996</v>
+        <v>732.6465622079998</v>
       </c>
       <c r="Q88">
-        <v>1656.863199424</v>
+        <v>1653.746562208</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2925323979295916</v>
+        <v>0.3102350746519392</v>
       </c>
       <c r="T88">
-        <v>3.215750266400879</v>
+        <v>3.446475488802124</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.745069588431029</v>
+        <v>3.702022811552512</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07208381970475208</v>
+        <v>0.07182482369936136</v>
       </c>
       <c r="C89">
-        <v>6839.491789212222</v>
+        <v>6891.918401607445</v>
       </c>
       <c r="D89">
-        <v>13848.49578921222</v>
+        <v>13986.31440160745</v>
       </c>
       <c r="E89">
-        <v>4556.404</v>
+        <v>4641.796000000001</v>
       </c>
       <c r="F89">
-        <v>7429.104</v>
+        <v>7514.496000000001</v>
       </c>
       <c r="G89">
         <v>420.1</v>
@@ -8591,28 +8591,28 @@
         <v>1520.9</v>
       </c>
       <c r="M89">
-        <v>410.8294512000001</v>
+        <v>415.5516288000001</v>
       </c>
       <c r="N89">
-        <v>1110.0705488</v>
+        <v>1105.3483712</v>
       </c>
       <c r="O89">
-        <v>377.4239865919999</v>
+        <v>375.8184462079998</v>
       </c>
       <c r="P89">
-        <v>732.6465622079998</v>
+        <v>729.5299249919997</v>
       </c>
       <c r="Q89">
-        <v>1653.746562208</v>
+        <v>1650.629924992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3102350746519392</v>
+        <v>0.330888197494678</v>
       </c>
       <c r="T89">
-        <v>3.446475488802124</v>
+        <v>3.715654914936912</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.702022811552512</v>
+        <v>3.659954370512142</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07182482369936136</v>
+        <v>0.07156582769397063</v>
       </c>
       <c r="C90">
-        <v>6891.918401607445</v>
+        <v>6947.115696978803</v>
       </c>
       <c r="D90">
-        <v>13986.31440160745</v>
+        <v>14126.9036969788</v>
       </c>
       <c r="E90">
-        <v>4641.796000000001</v>
+        <v>4727.188000000001</v>
       </c>
       <c r="F90">
-        <v>7514.496000000001</v>
+        <v>7599.888000000001</v>
       </c>
       <c r="G90">
         <v>420.1</v>
@@ -8673,28 +8673,28 @@
         <v>1520.9</v>
       </c>
       <c r="M90">
-        <v>415.5516288000001</v>
+        <v>420.2738064000001</v>
       </c>
       <c r="N90">
-        <v>1105.3483712</v>
+        <v>1100.6261936</v>
       </c>
       <c r="O90">
-        <v>375.8184462079998</v>
+        <v>374.2129058239999</v>
       </c>
       <c r="P90">
-        <v>729.5299249919997</v>
+        <v>726.4132877759997</v>
       </c>
       <c r="Q90">
-        <v>1650.629924992</v>
+        <v>1647.513287776</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.330888197494678</v>
+        <v>0.3552964335815512</v>
       </c>
       <c r="T90">
-        <v>3.715654914936912</v>
+        <v>4.033776054914387</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.659954370512142</v>
+        <v>3.618831287697399</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07156582769397063</v>
+        <v>0.07130683168857987</v>
       </c>
       <c r="C91">
-        <v>6947.115696978803</v>
+        <v>7005.168075752646</v>
       </c>
       <c r="D91">
-        <v>14126.9036969788</v>
+        <v>14270.34807575265</v>
       </c>
       <c r="E91">
-        <v>4727.188000000001</v>
+        <v>4812.580000000001</v>
       </c>
       <c r="F91">
-        <v>7599.888000000001</v>
+        <v>7685.280000000001</v>
       </c>
       <c r="G91">
         <v>420.1</v>
@@ -8755,28 +8755,28 @@
         <v>1520.9</v>
       </c>
       <c r="M91">
-        <v>420.2738064000001</v>
+        <v>424.9959840000001</v>
       </c>
       <c r="N91">
-        <v>1100.6261936</v>
+        <v>1095.904016</v>
       </c>
       <c r="O91">
-        <v>374.2129058239999</v>
+        <v>372.6073654399999</v>
       </c>
       <c r="P91">
-        <v>726.4132877759997</v>
+        <v>723.2966505599996</v>
       </c>
       <c r="Q91">
-        <v>1647.513287776</v>
+        <v>1644.39665056</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3552964335815512</v>
+        <v>0.3845863168857989</v>
       </c>
       <c r="T91">
-        <v>4.033776054914387</v>
+        <v>4.415521422887358</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.618831287697399</v>
+        <v>3.578622051167428</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07130683168857987</v>
+        <v>0.07104783568318913</v>
       </c>
       <c r="C92">
-        <v>7005.168075752646</v>
+        <v>7066.163401523161</v>
       </c>
       <c r="D92">
-        <v>14270.34807575265</v>
+        <v>14416.73540152316</v>
       </c>
       <c r="E92">
-        <v>4812.580000000001</v>
+        <v>4897.972000000001</v>
       </c>
       <c r="F92">
-        <v>7685.280000000001</v>
+        <v>7770.672</v>
       </c>
       <c r="G92">
         <v>420.1</v>
@@ -8837,28 +8837,28 @@
         <v>1520.9</v>
       </c>
       <c r="M92">
-        <v>424.9959840000001</v>
+        <v>429.7181616</v>
       </c>
       <c r="N92">
-        <v>1095.904016</v>
+        <v>1091.1818384</v>
       </c>
       <c r="O92">
-        <v>372.6073654399999</v>
+        <v>371.0018250559999</v>
       </c>
       <c r="P92">
-        <v>723.2966505599996</v>
+        <v>720.1800133439997</v>
       </c>
       <c r="Q92">
-        <v>1644.39665056</v>
+        <v>1641.280013344</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3845863168857989</v>
+        <v>0.4203850631465462</v>
       </c>
       <c r="T92">
-        <v>4.415521422887358</v>
+        <v>4.882099094854322</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.578622051167428</v>
+        <v>3.539296534121632</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07104783568318913</v>
+        <v>0.07078883967779841</v>
       </c>
       <c r="C93">
-        <v>7066.163401523161</v>
+        <v>7130.193180521847</v>
       </c>
       <c r="D93">
-        <v>14416.73540152316</v>
+        <v>14566.15718052185</v>
       </c>
       <c r="E93">
-        <v>4897.972000000001</v>
+        <v>4983.364000000001</v>
       </c>
       <c r="F93">
-        <v>7770.672</v>
+        <v>7856.064000000001</v>
       </c>
       <c r="G93">
         <v>420.1</v>
@@ -8919,28 +8919,28 @@
         <v>1520.9</v>
       </c>
       <c r="M93">
-        <v>429.7181616</v>
+        <v>434.4403392000001</v>
       </c>
       <c r="N93">
-        <v>1091.1818384</v>
+        <v>1086.459660799999</v>
       </c>
       <c r="O93">
-        <v>371.0018250559999</v>
+        <v>369.3962846719999</v>
       </c>
       <c r="P93">
-        <v>720.1800133439997</v>
+        <v>717.0633761279996</v>
       </c>
       <c r="Q93">
-        <v>1641.280013344</v>
+        <v>1638.163376128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4203850631465462</v>
+        <v>0.4651334959724804</v>
       </c>
       <c r="T93">
-        <v>4.882099094854322</v>
+        <v>5.465321184813028</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.539296534121632</v>
+        <v>3.50082591962031</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07078883967779841</v>
+        <v>0.07052984367240767</v>
       </c>
       <c r="C94">
-        <v>7130.193180521847</v>
+        <v>7197.352752364496</v>
       </c>
       <c r="D94">
-        <v>14566.15718052185</v>
+        <v>14718.7087523645</v>
       </c>
       <c r="E94">
-        <v>4983.364000000001</v>
+        <v>5068.756000000001</v>
       </c>
       <c r="F94">
-        <v>7856.064000000001</v>
+        <v>7941.456000000001</v>
       </c>
       <c r="G94">
         <v>420.1</v>
@@ -9001,28 +9001,28 @@
         <v>1520.9</v>
       </c>
       <c r="M94">
-        <v>434.4403392000001</v>
+        <v>439.1625168</v>
       </c>
       <c r="N94">
-        <v>1086.459660799999</v>
+        <v>1081.7374832</v>
       </c>
       <c r="O94">
-        <v>369.3962846719999</v>
+        <v>367.7907442879999</v>
       </c>
       <c r="P94">
-        <v>717.0633761279996</v>
+        <v>713.9467389119998</v>
       </c>
       <c r="Q94">
-        <v>1638.163376128</v>
+        <v>1635.046738912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4651334959724804</v>
+        <v>0.52266719532011</v>
       </c>
       <c r="T94">
-        <v>5.465321184813028</v>
+        <v>6.215178157617078</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.50082591962031</v>
+        <v>3.463182630162027</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07052984367240767</v>
+        <v>0.07027084766701693</v>
       </c>
       <c r="C95">
-        <v>7197.352752364496</v>
+        <v>7267.741492911146</v>
       </c>
       <c r="D95">
-        <v>14718.7087523645</v>
+        <v>14874.48949291115</v>
       </c>
       <c r="E95">
-        <v>5068.756000000001</v>
+        <v>5154.148000000001</v>
       </c>
       <c r="F95">
-        <v>7941.456000000001</v>
+        <v>8026.848000000001</v>
       </c>
       <c r="G95">
         <v>420.1</v>
@@ -9083,28 +9083,28 @@
         <v>1520.9</v>
       </c>
       <c r="M95">
-        <v>439.1625168</v>
+        <v>443.8846944000001</v>
       </c>
       <c r="N95">
-        <v>1081.7374832</v>
+        <v>1077.015305599999</v>
       </c>
       <c r="O95">
-        <v>367.7907442879999</v>
+        <v>366.1852039039998</v>
       </c>
       <c r="P95">
-        <v>713.9467389119998</v>
+        <v>710.8301016959997</v>
       </c>
       <c r="Q95">
-        <v>1635.046738912</v>
+        <v>1631.930101696</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.52266719532011</v>
+        <v>0.5993787944502827</v>
       </c>
       <c r="T95">
-        <v>6.215178157617078</v>
+        <v>7.214987454689146</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.463182630162027</v>
+        <v>3.426340261756048</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07027084766701693</v>
+        <v>0.07001185166162618</v>
       </c>
       <c r="C96">
-        <v>7267.741492911146</v>
+        <v>7341.463030146149</v>
       </c>
       <c r="D96">
-        <v>14874.48949291115</v>
+        <v>15033.60303014615</v>
       </c>
       <c r="E96">
-        <v>5154.148000000001</v>
+        <v>5239.540000000002</v>
       </c>
       <c r="F96">
-        <v>8026.848000000001</v>
+        <v>8112.240000000002</v>
       </c>
       <c r="G96">
         <v>420.1</v>
@@ -9165,28 +9165,28 @@
         <v>1520.9</v>
       </c>
       <c r="M96">
-        <v>443.8846944000001</v>
+        <v>448.6068720000001</v>
       </c>
       <c r="N96">
-        <v>1077.015305599999</v>
+        <v>1072.293128</v>
       </c>
       <c r="O96">
-        <v>366.1852039039998</v>
+        <v>364.5796635199999</v>
       </c>
       <c r="P96">
-        <v>710.8301016959997</v>
+        <v>707.7134644799996</v>
       </c>
       <c r="Q96">
-        <v>1631.930101696</v>
+        <v>1628.81346448</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5993787944502827</v>
+        <v>0.7067750332325248</v>
       </c>
       <c r="T96">
-        <v>7.214987454689146</v>
+        <v>8.614720470590042</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.426340261756048</v>
+        <v>3.390273522158616</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07001185166162618</v>
+        <v>0.06975285565623546</v>
       </c>
       <c r="C97">
-        <v>7341.463030146149</v>
+        <v>7418.625474063745</v>
       </c>
       <c r="D97">
-        <v>15033.60303014615</v>
+        <v>15196.15747406375</v>
       </c>
       <c r="E97">
-        <v>5239.540000000002</v>
+        <v>5324.932000000002</v>
       </c>
       <c r="F97">
-        <v>8112.240000000002</v>
+        <v>8197.632000000001</v>
       </c>
       <c r="G97">
         <v>420.1</v>
@@ -9247,28 +9247,28 @@
         <v>1520.9</v>
       </c>
       <c r="M97">
-        <v>448.6068720000001</v>
+        <v>453.3290496000001</v>
       </c>
       <c r="N97">
-        <v>1072.293128</v>
+        <v>1067.5709504</v>
       </c>
       <c r="O97">
-        <v>364.5796635199999</v>
+        <v>362.9741231359999</v>
       </c>
       <c r="P97">
-        <v>707.7134644799996</v>
+        <v>704.5968272639998</v>
       </c>
       <c r="Q97">
-        <v>1628.81346448</v>
+        <v>1625.696827264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7067750332325248</v>
+        <v>0.867869391405888</v>
       </c>
       <c r="T97">
-        <v>8.614720470590042</v>
+        <v>10.71431999444139</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.390273522158616</v>
+        <v>3.354958172969464</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06975285565623546</v>
+        <v>0.06949385965084472</v>
       </c>
       <c r="C98">
-        <v>7418.625474063747</v>
+        <v>7499.34166163085</v>
       </c>
       <c r="D98">
-        <v>15196.15747406375</v>
+        <v>15362.26566163085</v>
       </c>
       <c r="E98">
-        <v>5324.932</v>
+        <v>5410.324000000001</v>
       </c>
       <c r="F98">
-        <v>8197.632</v>
+        <v>8283.024000000001</v>
       </c>
       <c r="G98">
         <v>420.1</v>
@@ -9329,28 +9329,28 @@
         <v>1520.9</v>
       </c>
       <c r="M98">
-        <v>453.3290496</v>
+        <v>458.0512272000001</v>
       </c>
       <c r="N98">
-        <v>1067.5709504</v>
+        <v>1062.8487728</v>
       </c>
       <c r="O98">
-        <v>362.9741231359999</v>
+        <v>361.3685827519999</v>
       </c>
       <c r="P98">
-        <v>704.5968272639998</v>
+        <v>701.4801900479997</v>
       </c>
       <c r="Q98">
-        <v>1625.696827264</v>
+        <v>1622.580190048</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8678693914058857</v>
+        <v>1.13635998836149</v>
       </c>
       <c r="T98">
-        <v>10.71431999444136</v>
+        <v>14.21365253419358</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.354958172969464</v>
+        <v>3.320370975309985</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06949385965084472</v>
+        <v>0.06923486364545398</v>
       </c>
       <c r="C99">
-        <v>7499.34166163085</v>
+        <v>7583.729417993354</v>
       </c>
       <c r="D99">
-        <v>15362.26566163085</v>
+        <v>15532.04541799335</v>
       </c>
       <c r="E99">
-        <v>5410.324000000001</v>
+        <v>5495.716000000001</v>
       </c>
       <c r="F99">
-        <v>8283.024000000001</v>
+        <v>8368.416000000001</v>
       </c>
       <c r="G99">
         <v>420.1</v>
@@ -9411,28 +9411,28 @@
         <v>1520.9</v>
       </c>
       <c r="M99">
-        <v>458.0512272000001</v>
+        <v>462.7734048000001</v>
       </c>
       <c r="N99">
-        <v>1062.8487728</v>
+        <v>1058.126595199999</v>
       </c>
       <c r="O99">
-        <v>361.3685827519999</v>
+        <v>359.7630423679998</v>
       </c>
       <c r="P99">
-        <v>701.4801900479997</v>
+        <v>698.3635528319996</v>
       </c>
       <c r="Q99">
-        <v>1622.580190048</v>
+        <v>1619.463552832</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.13635998836149</v>
+        <v>1.673341182272698</v>
       </c>
       <c r="T99">
-        <v>14.21365253419358</v>
+        <v>21.21231761369803</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.320370975309985</v>
+        <v>3.286489638827229</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.06923486364545398</v>
+        <v>0.06897586764006325</v>
       </c>
       <c r="C100">
-        <v>7583.729417993354</v>
+        <v>7671.911835196779</v>
       </c>
       <c r="D100">
-        <v>15532.04541799335</v>
+        <v>15705.61983519678</v>
       </c>
       <c r="E100">
-        <v>5495.716000000001</v>
+        <v>5581.108000000001</v>
       </c>
       <c r="F100">
-        <v>8368.416000000001</v>
+        <v>8453.808000000001</v>
       </c>
       <c r="G100">
         <v>420.1</v>
@@ -9493,28 +9493,28 @@
         <v>1520.9</v>
       </c>
       <c r="M100">
-        <v>462.7734048000001</v>
+        <v>467.4955824</v>
       </c>
       <c r="N100">
-        <v>1058.126595199999</v>
+        <v>1053.4044176</v>
       </c>
       <c r="O100">
-        <v>359.7630423679998</v>
+        <v>358.1575019839999</v>
       </c>
       <c r="P100">
-        <v>698.3635528319996</v>
+        <v>695.2469156159997</v>
       </c>
       <c r="Q100">
-        <v>1619.463552832</v>
+        <v>1616.346915615999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.673341182272698</v>
+        <v>3.284284764006322</v>
       </c>
       <c r="T100">
-        <v>21.21231761369803</v>
+        <v>42.20831285221139</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.286489638827229</v>
+        <v>3.253292773788571</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06897586764006325</v>
-      </c>
-      <c r="C101">
-        <v>7671.911835196779</v>
-      </c>
-      <c r="D101">
-        <v>15705.61983519678</v>
-      </c>
-      <c r="E101">
-        <v>5581.108000000001</v>
-      </c>
-      <c r="F101">
-        <v>8453.808000000001</v>
-      </c>
-      <c r="G101">
-        <v>420.1</v>
-      </c>
-      <c r="H101">
-        <v>5666.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2442</v>
-      </c>
-      <c r="K101">
-        <v>921.0999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1520.9</v>
-      </c>
-      <c r="M101">
-        <v>467.4955824</v>
-      </c>
-      <c r="N101">
-        <v>1053.4044176</v>
-      </c>
-      <c r="O101">
-        <v>358.1575019839999</v>
-      </c>
-      <c r="P101">
-        <v>695.2469156159997</v>
-      </c>
-      <c r="Q101">
-        <v>1616.346915615999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.284284764006322</v>
-      </c>
-      <c r="T101">
-        <v>42.20831285221139</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.34</v>
-      </c>
-      <c r="W101">
-        <v>0.036498</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.253292773788571</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
